--- a/IOM.xlsx
+++ b/IOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12055,6 +12055,4819 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>50,000 People Cross into Kenya Fleeing Violence in Ethiopia, IOM Says</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/50000-people-cross-kenya-fleeing-violence-ethiopia-iom-says</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+28 October 2026
+Geneva/Nairobi, 29 October 2026 – Approximately 50,000 people have crossed into northern Kenya following violent clashes in neighbouring Ethiopia, the International Organization for Migration (IOM) said, warning that further arrivals could place additional pressure on already stretched local services and resources.
+With the situation continuing to evolve, the Government of Kenya and inter-agency partners are planning for a response covering up to 80,000 people in anticipation of further arrivals and growing humanitarian needs.
+“Thousands of people have crossed into Kenya seeking safety, and most are being sheltered by local communities. The situation remains fluid, and the numbers of arrivals could increase in the coming days. Meeting their immediate needs, while also supporting the communities who are now hosting thousands, is an urgent priority,” said Nomagugu Ncube, IOM Kenya Chief of Mission.
+As of 29 October, an estimated 50,000 people had arrived in Moyale, Marsabit County. Those arriving are staying with local communities along the border, while others are sheltering across five temporary sites. Communities hosting new arrivals are already facing pressure on resources and services, which could worsen if more people cross the border. Those arriving need water, shelter, healthcare and basic supplies. Protection and sanitation services are also among the immediate needs identified.
+As part of the wider UN humanitarian response, IOM is working with the Government of Kenya, UNHCR, the Department of Refugee Services and other humanitarian partners to monitor cross-border movements, assess displacement and address priority needs.
+IOM is supporting assessments through its Displacement Tracking Matrix, which collects information about displaced people to help identify priority needs and guide assistance. Arrival figures remain preliminary and may change as more information becomes available.
+Working with national and county authorities and partners, IOM is also planning an emergency response which would support shelter and essential household items, targeted emergency shelter for the most vulnerable families, water tanks and water purifying tablets, and assessments and monitoring.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:48:41.854962+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Thousands Flee Yemen by Sea as Displacement Tops 268,000</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/thousands-flee-yemen-sea-displacement-tops-268000</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Aden, 23 October 2026 – Escalating conflict in western Yemen is driving people beyond the country's borders, with thousands fleeing by sea to Djibouti. New data from the International Organization for Migration (IOM) shows the crisis's impact beyond Yemen's borders. As of 17 October, 3,836 Yemenis have arrived in Djibouti, half of them children, including 282 under the age of five. Most report fleeing worsening insecurity, with several boats reportedly coming ashore short of their destination after running out of fuel. IOM also recorded 1,327 migrants crossing from Yemen to Djibouti by sea as they returned towards their countries of residence.
+At the same time, displacement inside Yemen has continued to rise. As of 23 October, more than 268,000 people had been displaced, almost all of them since the beginning of September. Families are increasingly seeking safety farther south. In Aden, the number of displaced people has more than doubled since 7 October to more than 42,000, while Lahj now hosts around 67,000. Displaced families are now sheltering in 62 districts across ten governorates, as far east as Al Maharah.
+"The scale and speed of this displacement is leaving families in desperate need of help, and our response is struggling to keep pace," said Abdusattor Esoev, IOM Yemen Chief of Mission. "Our teams are reaching people every day, but funding is falling far short. Without urgent support, more families will go without assistance that could save their lives."
+With 44,736 families displaced, many are struggling to access clean water, health care and basic services amid severe fuel shortages and skyrocketing prices for basic food items and medicine. Families are sheltering in overcrowded public buildings or sleeping in the open, often without adequate sanitation. Women, children, older people and people with disabilities face heightened protection risks, while humanitarian access constraints in Ta'iz continue to slow aid delivery.
+IOM faces a critical funding gap of USD 30 million over the next six months to provide shelter, emergency cash, protection, health care, clean water and sanitation, and to track displacement. The response is being delivered through the Yemen Crisis Response Plan 2026, which supports displaced families and host communities in Yemen, and the Regional Migrant Response Plan for the Horn of Africa and Yemen, which supports migrants travelling from the Horn of Africa and through Yemen.
+"Many families have had to flee more than once, each time facing the struggle to find somewhere safe to stay and access the support they need," said Esoev. "Support must reach both displaced families and the communities hosting them now, before more lives are put at risk."
+Since 1 August, IOM has worked with local authorities, UN partners and local organizations to reach 11,178 conflict-affected households with emergency shelter, household items, water, sanitation and hygiene supplies and multi-purpose cash assistance. IOM has also provided protection services to 6,757 migrants and displaced people and carried out 56,863 primary health care consultations.
+IOM calls on donors to urgently scale up support to keep pace with rapidly growing needs, and on all parties to protect civilians and humanitarian workers and to ensure safe, unimpeded access to people in need.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+Note to Editors:
+Arrival figures for Yemeni nationals in Djibouti are based on registration data from the Djiboutian authorities (Office National d’Assistance aux Réfugiés et Sinistrés, ONARS) and the UN Refugee Agency (UNHCR). Figures on migrants returning from Yemen by sea were recorded through IOM’s flow monitoring in Djibouti.
+Both are drawn from IOM's Escalation in the Middle East and Beyond: Mobility Report, published on 22 October 2026 by IOM’s Displacement Tracking Matrix.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:48:48.710958+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Over 100 Skilled Workers Reach Italy Through Labour Mobility Scheme</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/over-100-skilled-workers-reach-italy-through-labour-mobility-scheme</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/ Rome, 21 October 2026 - As Italian companies face growing shortages of skilled workers, a labour mobility scheme linking Italy, Tunisia and Morocco has reached an important milestone. More than 100 skilled workers have arrived in Italy through the European Union (EU) Talent Partnerships framework, supported by the International Organization for Migration (IOM).
+"These arrivals show what is possible when labour mobility is planned, skills-based and shaped through genuine cooperation between countries of origin and destination. Workers are filling real labour market needs in Italy while gaining opportunities to use and develop their skills creating long-term benefits for workers, employers and communities.” Said Salvatore Sortino, Director of the IOM Coordination Office for the Mediterranean.
+Last week, 35 Moroccan mechatronics technicians, arrived in Italy, landing in Milan and Venice. This brings to 121 the total number of Moroccan and Tunisian workers who have arrived in Italy under the programme. From Morocco, 47 workers are now employed by 14 companies in Lombardy, Veneto and Emilia-Romagna, nine of which welcomed the latest arrivals. From Tunisia, 74 workers have been hired by 11 construction companies across Italy.
+These arrivals mark another step in THAMM Plus (Towards a Holistic Approach to Labour Migration Governance and Labour Mobility in Italy and North Africa), a programme co-funded by the European Union and the Italian Ministry of Interior and implemented by IOM. The initiative contributes to skills development and skills-based migration between North African countries and Italy, facilitating employment opportunities for 2,000 Tunisian workers in construction and 500 Moroccan workers in mechatronics.
+The initiative responds to significant and growing labour market needs in Italy and in partner countries. According to Unioncamere’s Excelsior data, Italian businesses are expected to require between 3.3 and 3.7 million workers by 2029, with around 617,000 positions projected to be filled by foreign workers. Priority sectors have been jointly identified with Morocco and Tunisia through the Talent Partnerships roundtables.
+THAMM Plus combines skills development with regular labour mobility, supporting workers from pre-departure training in their home country to inclusion in the Italian workplace, while promoting fair recruitment and stronger labour migration governance. Once matched with an employer, foreign workers enter Italy under Article 23 of the Consolidated Immigration Act, which allows those who complete approved vocational and civic-linguistic training at home to work in Italy outside the annual quotas.
+"Behind every arrival is a person who has invested in developing their skills and an employer seeking talent. When these skills are matched through safe and regular pathways, people move safely, arrive prepared and have a real chance to contribute and belong," Sortino added.
+The Italian experience shows that mobility works best when the whole ecosystem works together with verified demand, employer readiness, responsive training, skills recognition, streamlined admission, ethical recruitment and welcoming communities. These lessons are relevant to current and future EU Talent Partnerships.
+Through this approach, labour mobility becomes more than a response to immediate vacancies: it becomes a long-term investment in terms of skills, stronger labour market cooperation and development across both shores of the Mediterranean.
+With more workers set to arrive in the coming months, the initiative continues to demonstrate how regular migration pathways can help respond to labour needs, create opportunities for skills development and economic growth in countries of origin and destination, whilst supporting people to move safely and build sustainable opportunities.
+Notes to editors
+THAMM Plus is a transregional programme running from 2024 to 2027, co-funded by the European Union and the Italian Ministry of Interior, and implemented by IOM in Tunisia, Morocco and Italy.
+In Italy, THAMM Plus works with the Ministry of Labour and Social Policies, including the Directorate-General for Migration Policies and the Social and Labour Inclusion of Migrants. In Tunisia, partners include the Ministry of Employment and Vocational Training, ANETI, and ATFP. In Morocco, the partners are ANAPEC, MIEPEEC, OFPPT and IFMIA. Labour-market figures are based on Medium-term forecasts of employment and occupational needs in Italy (2025–2029), produced by Unioncamere, Italy’s national association of Chambers of Commerce, through its Excelsior labour-market information system, in collaboration with the Ministry of Labour and Social Policies.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:48:56.020977+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Over 800,000 People at Risk of Displacement as Floods Threaten Somalia, IOM Warns</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/over-800000-people-risk-displacement-floods-threaten-somalia-iom-warns</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+21 October 2026
+Geneva/Mogadishu, 21 October 2026 – Nearly 874,000 people could be forced from their homes in Somalia over the next three months, due to flooding, the International Organization for Migration (IOM) warned, as rising rivers and heavy rainfall threaten communities already struggling with drought and repeated displacement. 
+“We are looking at the possibility of hundreds of thousands of people losing their homes in just a matter of weeks. Many of these families have already been displaced before and have very little left to fall back on,” said Manuel Marques Pereira, IOM Somalia Chief of Mission. “There is still time to reduce the impact, but that window is closing. We urgently need funding to help people protect their homes and livelihoods, reach safer ground where necessary, and avoid another cycle of displacement.” 
+New projections by IOM and the Danish Refugee Council (DRC) estimate that 874,319 people could be displaced between October and December, with flooding accounting for 92 per cent of the projected displacement. The warning comes as Somalia enters a rainy season forecast to bring above-normal rainfall amid strengthening El Niño conditions. 
+Despite the growing threat, IOM has secured only about 14.4 per cent of the required USD 16.62 million needed to prepare for and respond to El Niño-related flooding. The funding is intended to support more than 517,000 people in flood-prone communities across Somalia.
+Signs of flooding are already emerging. In Dollow, the Jubba River is approaching flood levels, while the Shabelle River is rising towards the top of its banks in Jowhar. Heavy rainfall in Baidoa has already damaged homes and forced families to flee several neighbourhoods. 
+Beletweyne and Gaalkacyo are among the areas facing the greatest threat, with approximately 229,000 and 82,000 people respectively at risk of displacement. Families living in overcrowded displacement sites are particularly vulnerable, with assessments identifying inadequate access to safe water and sanitation, raising concerns about disease outbreaks if flooding intensifies. 
+Beyond the immediate threat to homes, rising floodwaters could destroy crops, disrupt livelihoods, contaminate water sources and cut off access to healthcare and other essential services, deepening humanitarian needs in communities already affected by successive climate shocks. 
+IOM is working with Somali authorities and local communities to strengthen early warning systems, identify safer evacuation routes and prepare emergency assistance. However, funding shortages are limiting efforts to establish safe relocation areas and provide essential shelter, clean water, sanitation and healthcare. 
+IOM is calling for urgent international support to scale up preparedness and early action before rising floodwaters force more families from their homes. 
+For more information, please contact IOM Media Center
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:03.058582+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Damaged Homes and Energy Attacks Risk Displacing Ukrainians Again this Winter, IOM Warns</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/damaged-homes-and-energy-attacks-risk-displacing-ukrainians-again-winter-iom-warns-0</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Kyiv, 16 October 2026 – Ukrainians who returned home after fleeing war risk being displaced again this winter, as damaged housing, repeated attacks on energy infrastructure and unaffordable heating leave families with few alternatives, the International Organization for Migration (IOM) warned today.
+"For millions of Ukrainians, the challenge is no longer simply whether they can return home. It is whether they can remain there safely and right now the conditions are making it difficult," said Arthur Erken, IOM Regional Director for Europe and Central Asia.
+According to IOM's latest findings, intentions to leave again are highest among those who returned within the previous three months.
+More than four years into the full-scale war, families and communities have exhausted much of their capacity to cope with further shocks. Repeated attacks on energy infrastructure have weakened essential services, while damaged homes and limited incomes make recovery increasingly difficult.
+Shelter needs are substantial. An estimated 1.45 million returnees now live in frontline districts, including 565,000 in Kharkiv region alone. In rural frontline areas, three in four returnees need materials to repair damaged walls, while nearly two in three require roofing materials and insulation.
+Even where heating is available, many families cannot afford it. During the last cold season, only 32 per cent of households reported being able to heat their homes adequately, falling to just one in four in frontline areas. Nearly six in ten households reduced heating consumption to save money.
+The risks extend beyond frontline communities. Six in ten residents of large cities depend on district heating, while one fifth of urban households have no backup power source. An estimated 2.1 million older people live alone in multi-apartment buildings, leaving many particularly exposed to prolonged heating and electricity disruptions.
+Nearly 3.6 million people remain internally displaced across Ukraine, while an estimated 3.8 million have returned to their places of residence after displacement since February 2022.
+“With winter approaching, the window to act is narrowing. Less than 7 per cent of IOM’s Ukraine Crisis Response Plan for 2026 has been funded, severely limiting the assistance available ahead of winter. Additional support is critical now, before winter conditions deepen existing needs and put more families at risk of displacement,” added Erken.
+IOM is calling for urgent support to repair damaged homes, improve insulation and maintain essential services, alongside investment in sustainable, decentralized energy solutions to help communities withstand future disruptions.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:09.973775+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>IOM Chief Says Demographic Shifts Driving Need for Indian Talent</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-chief-says-demographic-shifts-driving-need-indian-talent</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+New Delhi, 16 October 2026 — The world is looking to India for talent as more of its leading economies are ageing. The International Organization for Migration (IOM) Director General Amy Pope highlighted in New Delhi today the importance of expanding safe and regular pathways for labour mobility and strengthening cooperation on skills recognition and worker protection. Safe, fair labour mobility can make sure everyone gains, and IOM can play a key role in making that happen. 
+"Walk into a hospital, a building site or a tech company almost anywhere in the world, and there's a good chance you'll meet someone from India," said DG Pope. "The world already runs on Indian talent. Our job is to make sure everyone who leaves home to work does it safely — and comes back stronger." 
+India has about one billion people of working age. Its median age is 29. Many other countries are ageing fast, and their workforces are shrinking. 
+About 18.5 million people born in India live abroad. It is the largest diaspora in the world. Around half work in the Gulf. In 2024, India received USD 137.67 billion in remittances from people living and working abroad more than any other country, according to IOM's World Migration Report 2026. These transfers provide a vital source of money to pay for education, health care and homes for millions of families.  
+Demand is growing in other places too. In 2024, Indians received one in five European Union Blue Cards for highly skilled workers, more than any other nationality. Germany has raised its yearly quota of skilled-worker visas for Indians from 20,000 to 90,000. 
+India has built a growing network of migration and mobility partnerships and labour mobility arrangements with partner countries. Building on this architecture, IOM can support government efforts to connect labour-market demand in destination countries with talent across India.
+India has already built an ambitious network of mobility partnerships," said DG Pope. "The opportunity now is to deepen their impact so that a young Indian nurse can have her skills recognized and access a job abroad fairly and safely."
+India has put important systems in place. Its e-Migrate platform regulates overseas recruitment and has issued more than five million clearances. Workers get training before they leave, and support if they face a crisis abroad.
+Labour mobility also takes place within India, as people move between states and regions in search of work, skills development and economic opportunity. Ensuring fair recruitment, decent working conditions and access to protection for workers on the move is important both within India and across international borders.
+IOM can help advance these efforts. It works with the Government, destination countries, employers and workers, so that everyone benefits. IOM helps employers and recruiters hire ethically, so that workers don’t have to pay fees to get a job. Reducing recruitment and money-transfer costs can help ensure that more of the benefits of migration reach workers and their families.
+IOM also supports cooperation with destination countries for the recognition of Indian skills, while helping workers know their rights, prepare for life abroad and look after their well-being. This way, we maximize diaspora contributions, migrants' skills and returnees' experience to support investment and economic development.  
+As fake job offers online lure people, including Indian nationals, into scam centres and forced labour abroad, IOM works to protect people from harm. IOM works with governments to raise awareness, identify and support victims of trafficking, and help them return home safely. IOM also uses data and technology to understand how climate change affects where people live and work, helping communities prepare and adapt. 
+"If a job offer sounds too good to be true, it usually is," said DG Pope. "No one should lose their savings, or their freedom, chasing a dream job." 
+"Safe migration is a team effort," she added. "Governments set the rules, employers play fair, and IOM makes sure no worker is left on their own. When everyone does their part, the worker wins, the family wins, and so do the countries on both ends." 
+This is DG Pope's first visit to India as Director General. During the visit, she met Minister of State for External Affairs Kirti Vardhan Singh and Minister of State for Labour and Employment Shobha Karandlaje. They discussed advancing skills recognition and worker protection. 
+India has been an IOM Member State since 2008. 
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:17.133931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Two Months After Colombia Earthquake, Funding Gap Puts 57,000 at Risk as El Niño Intensifies</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/two-months-after-colombia-earthquake-funding-gap-puts-57000-risk-el-nino-intensifies</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Bogotá, 15 October 2026 - Families still recovering from a magnitude 7.4 earthquake that affected nearly 487,000 people in western Colombia now face a strengthening El Niño expected to persist into 2027. With its emergency appeal less than a quarter funded, the International Organization for Migration (IOM) warns that at least 57,000 people could be left without critical assistance, including housing, water, health care and protection.
+IOM launched a USD 30 million flash appeal on 20 August, but only USD 6.5 million has been secured. The funding received will support assistance for around 43,000 people, against a target of up to 100,000.
+“Two months on, the emergency is far from over for hundreds of thousands of people in Colombia,” said Juan Francisco Espinosa, IOM Regional Director for Latin America and the Caribbean. “Families who lost their homes now face a second shock as El Niño intensifies. Working with the Colombian Government and our partners, we can help families secure safe housing and rebuild livelihoods, but we need urgent funding while it can still make a difference.”
+The earthquake of 10 August caused widespread damage to homes, infrastructure and essential services across western Colombia. Although approximately 2,700 people remain in temporary shelters, many more earthquake-affected households need support to repair their homes, restore livelihoods, and regain access to basic services.
+On 8 October, Colombia's national meteorological authority, IDEAM, officially confirmed El Niño conditions and warned of risks including water shortages, wildfires, livelihood losses and disruption to essential services. The forecast adds to the pressure on communities still recovering from the earthquake.
+Public health and environmental risks add to the challenge facing earthquake-affected communities. According to Colombia’s National Institute of Health, dengue cases rose by more than 30 per cent in September in Chocó, Risaralda and Valle del Cauca, while wildfires burned more than 26,500 hectares across the country. Sudden downpours risk triggering landslides on slopes weakened by the earthquake.
+According to Colombia’s disaster response agency, UNGRD, the 10 August earthquake killed 335 people, left more than 100 missing, damaged nearly 207,000 homes and destroyed 36,000 across 16 departments. More than 286,000 children are still attending classes in temporary arrangements. An IOM assessment found that 87 per cent of affected municipalities are above the national average for multidimensional poverty. In remote areas such as Chocó, damage to roads and essential infrastructure has further disrupted access to basic services, food, markets and humanitarian assistance.
+Working with the Colombian Government and local authorities, IOM has moved from emergency relief to early recovery, assisting more than 10,000 people in 51 municipalities and prioritizing Afro-Colombian, Indigenous and rural communities in remote areas. IOM supports 25 of the 32 temporary shelters that still house 670 households, and helps families move to lasting housing through rental assistance, construction materials and repair guidance.
+IOM has also provided hygiene kits and water treatment units, deployed medical teams to hard-to-reach municipalities and supported more than 450 rescuers and responders with mental health care. In coordination with the Colombian Family Welfare Institute, IOM has set up child-friendly spaces and protection measures in shelters to help prevent trafficking, child recruitment, exploitation and gender-based violence.
+“The challenge now is to support families as they progressively move out of temporary shelters and rebuild their lives and communities through safe housing and sustainable livelihoods,” Espinosa said.
+IOM is calling for additional funding to help families secure safe housing, restore livelihoods and maintain access to essential services as El Nino strengthens.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:23.929588+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Over 4,400 Child Migrant Deaths Recorded Since 2014, True Toll Likely Much Higher</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/over-4400-child-migrant-deaths-recorded-2014-true-toll-likely-much-higher-0</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Berlin, 13 October – At least 4,414 children died during migration journeys worldwide between 2014 and 2025, and the true number is likely much higher, according to a new report by the Missing Migrants Project of the International Organization for Migration (IOM), supported by the International Data Alliance for Children on the Move (IDAC).
+Over the same period, IOM’s Missing Migrants Project recorded almost 81,000 migrant deaths and disappearances worldwide. Yet more than half of these records, 44,862 cases or 55.5 per cent, contain no information on age or age group. This means that an unknown number of children may be missing from the overall death toll. On the Central Mediterranean Route, for example, children accounted for 19 per cent of arrivals in Italy and Malta in 2024 but only 2 per cent of recorded deaths, highlighting gaps in demographic data and the extent to which child migrant deaths may remain invisible.
+“Every child who dies on a migration journey deserves to be counted, yet too many are missing from the data,” said Stuart Campo, Chief Strategy Officer for IOM’s Department of Data, Insight and Policy. “We cannot protect children from dangers we cannot see. Working with our fellow Secretariat members and partners in IDAC, we can close these gaps and give governments the evidence they need to save lives.”
+Children are often the least visible in migration data, even though they face a heightened risk of exploitation and other rights violations. Their deaths go uncounted in two ways. The “missing figure” refers to children whose deaths during migration are never recorded at all, while the “hidden figure” refers to deaths that are documented but lack the information needed to identify the person as a child. This especially affects teenagers, who may be mistakenly recorded as adults, leaving policymakers with limited evidence about the distinct risks children face during migration journeys. Together, these gaps mean that existing data almost certainly understate the scale of child deaths.
+Official records, such as those from medical examiners and law enforcement agencies, offer the most complete details on age, yet they account for only 18 per cent of all migrant deaths recorded by the Missing Migrants Project and just 820 of the 4,414 documented child deaths. Most other records come from humanitarian organizations, media reports and the testimonies of survivors and witnesses.
+The report calls on States to strengthen the documentation of migrant deaths, especially those of children. This means systematically recording the age and migration status of those who die, and improving data sharing among law enforcement, medical examiners and humanitarian organizations, while respecting data protection principles. It also recommends further testing of transparent, peer-reviewed statistical methods to estimate deaths that go unrecorded.
+“Continued advancements in data methods are essential to protecting the rights of children on the move,” said Marzia Rango, Migration and Displacement Programme Manager at UNICEF and IDAC Coordinator. “Not only can these help provide a clearer picture of the risks these children face, but also where action is most urgently needed. When new methods are used, however, we need to be clear about what they can – and cannot – tell us and ensure that child rights are safeguarded at all times.”
+The International Data Alliance for Children on the Move (IDAC) is a global coalition working to improve data on migrant and displaced children and support evidence-based policymaking. Jointly led by Eurostat, IOM, OECD, UNHCR and UNICEF, with UNICEF as Secretariat Chair and the European Union as its main donor, IDAC brings together governments, international organizations, civil society, academics and youth.
+Read the report: Documenting the Deaths of Child Migrants
+Explore IOM Missing Migrants Project data: https://missingmigrants.iom.int/data
+Learn more about IDAC: https://www.dataforchildrenonthemove.org/
+For more information, please visit IOM’s Media Centre.
+IDAC media contact: Marzia Rango, mrango@unicef.org
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:32.116153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>West African Arrivals to Europe Drop 59 Per Cent as Routes Turn Deadlier, New IOM Data</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/west-african-arrivals-europe-drop-59-cent-routes-turn-deadlier-new-iom-data</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+13 October 2026
+Geneva/Dakar, 13 October 2026 – Fewer people from West Africa are reaching Europe by sea, but the journey has not become safer. Arrivals from four major West African countries of origin fell by 59 per cent in the first half of 2026 compared with the same period in 2025, according to new data from the International Organization for Migration (IOM). However, the factors that drive migration remain, and dangerous journeys continue across multiple routes. 
+“Fewer arrivals in one place doesn’t mean the pressures have gone away,” said IOM Director General Amy Pope. “They often just shift to other routes. That’s why we need to look at the whole journey, from where people leave to where they arrive.” 
+A total of 4,566 people from Mali, Senegal, Guinea and The Gambia were registered arriving in Europe by sea during the first six months of 2026. The West African Atlantic Route (WAAR) remained the principal route, with West African nationals accounting for 83 per cent of arrivals registered in Jan-June 2026. This is followed by the Western Mediterranean Route (WMR) with 21.9 per cent (up from 15.6 per cent in 2025) and the Central Mediterranean Route (CMR), with 10.5 per cent (up from 8.6 per cent in 2025).  
+While absolute figures on arrivals are down, the increase in proportion of West African nationals across Mediterranean routes, points to a shifting migration landscape, underscoring the need to monitor developments across routes. 
+The decline comes amid ongoing joint efforts by countries of origin, transit and destination to strengthen migration governance and institutional capacity, expand protection and reintegration support, and deepen bilateral and regional cooperation. 
+However, the decline in arrivals presents only one side of the picture. Data on departures and interceptions indicate that people continue to attempt these journeys, underscoring that the drivers of irregular migration persist across routes, and that sustained action is key to reducing risks, expanding opportunities and making migration safer.  
+Pressure at key transit points between West Africa and Europe remains a critical concern, requiring sustained, focused and comprehensive joint efforts to address protection needs, support transit communities and make migration safer. 
+Data from the West African Atlantic Route show that while arrivals to the Canary Islands fell considerably since the 2024 peak (62 per cent decrease from 2024 to 2025), recorded deaths and disappearances remained broadly unchanged, falling 4 per cent from 2024 to 2025 (1,215 to 1,172), highlighting how the route has become much more dangerous for migrants. The geography of departures is also changing. Increased controls in traditional embarkation areas in Morocco, Mauritania and Senegal have contributed to a southward dispersion towards The Gambia, Guinea and Guinea-Bissau.  
+These alternative departure points can add up to 750 kilometres to the crossing, extending some journeys to approximately 2,200 kilometres and exposing people to longer periods at sea, more remote and less monitored coastlines, and greater risks of shipwreck, dehydration and disappearance. 
+“No single country can solve this alone,” Ms. Pope added. “We need to protect migrants wherever they are, create real opportunities for young people and work together across borders. When we do, lives are saved.” 
+The findings of the report reinforce why a comprehensive route-based approach is essential. Developments in one location can influence movements elsewhere, and migration dynamics cannot be fully understood through a single-country lens. Effective responses therefore need to connect protection, access to services, livelihoods and opportunities in communities of origin, support for migrants and communities in transit, and safe, orderly and regular migration pathways across countries of origin, transit and destination. 
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:39.189167+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Yemen: People Desperate to Flee Conflict While Thousands Arrive, All at Risk</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/yemen-people-desperate-flee-conflict-while-thousands-arrive-all-risk</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Aden/Geneva, 12 October 2026 – After over 139 people, including children, tragically died at sea off Djibouti on their way to Yemen, new data from the International Organization for Migration (IOM) shows a country caught in two crises. As of today, more than 217,000 people have fled their homes since fighting escalated on the West Coast. Yet migrants continue to arrive in dangerous journeys, in greater numbers than in recent years, crossing through Yemen looking for jobs and a better future.
+While many are being displaced due to conflict, migrant arrivals to Yemen are rising sharply. By the end of September, IOM recorded 134,100 migrants entering Yemen in 2026. That is already 22 per cent more than in all of 2025, when 110,144 arrived. It is more than double the 60,897 recorded in 2024.
+“In Yemen, families are desperate to escape their homes due to the conflict, while migrants continue to pass through the country seeking better future. Both are making dangerous journeys,” said IOM Director General Amy Pope. “Those who died off Djibouti knew the risks. They went anyway because they had no safe options. We need safer options, and we need them now.”
+As of 12 October, IOM’s Displacement Tracking Matrix (DTM) has recorded 217,303 displaced people, or 36,216 households. More than half of them, 55 per cent, are in Taiz Governorate. Most displacement sites there cannot be reached because of the ongoing conflict.
+The displacement is spreading. Lahj hosts the second-largest number, with 45,390 people, followed by Aden with 26,112. In Taiz, the hardest-hit districts are Jabal Habashi, with 32,346 people, Al Ma’afer, with 31,230, and Ash Shamayatayn, with 24,942. These districts have also seen some of the most intense hostilities in recent days.
+Migrants continue to arrive despite the ongoing conflict. In September alone, 11,841 migrants entered Yemen. More than 2,500 of them arrived through Taiz, even as hostilities intensified. Arrivals also rose in Abyan and Shabwah.
+“Two groups are on the move, in opposite directions. Yemeni families are fleeing to stay alive. Migrants are coming in search of a better future to cross through Yemen elsewhere. Both are risking their lives on dangerous routes,” said Ms. Pope.
+Most migrants arriving in Yemen on this route come from the Horn of Africa. Many hope to travel through Yemen to the Gulf countries in search of work. Instead, they face conflict, exploitation and abuse along the way. Many become stranded, with no money to go on and no safe way home.
+IOM calls on countries along this route to urgently work together to stop smugglers who profit from desperation, and to open safe, regular pathways so people do not have to gamble with their lives. Donors need to scale up their funding, because every day without support costs lives.
+For more information, please visit IOM’s Media Centre. 
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:45.983368+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Death Toll in Djibouti Shipwreck Climbs to 139, UN Migration</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/death-toll-djibouti-shipwreck-climbs-139-un-migration</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+11 October 2026
+Geneva/Obock 11 October 2026 – At least 139 migrants have died after their boat capsized off Djibouti, UN Migration (IOM) said today. Another 84 are still missing. The toll rose from 109 after 30 more bodies were recovered, and search and rescue efforts are continuing.
+The boat was carrying 305 people from Djibouti towards Yemen when it went down near Guehere, north of Obock, on the night of 8–9 October. It is one of the deadliest shipwrecks recorded on the Eastern Route.
+"No one gets into a boat like that unless they believe there is no other safe way," said IOM Director General Amy Pope. "We cannot keep treating these deaths as normal. Safe and legal pathways save lives. I am asking governments and donors to act before the next boat goes down."
+Djiboutian authorities continue search and recovery operations as fears grow for those still missing. About 82 people survived the shipwreck. 
+IOM is providing emergency assistance to survivors at its Migrant Response Centre in Obock, including healthcare, psychosocial support, food, shelter and protection services.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:53.013454+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>109 Including 15 Children Dead, Over 116 Missing in Deadliest Shipwreck off Djibouti</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/109-including-15-children-dead-over-116-missing-deadliest-shipwreck-djibouti</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Obock, 11 October 2026 – At least 109 migrants, including 15 children, have died and more than 116 others remain missing after a boat carrying 305 capsized the International Organization for Migration (IOM) said today.
+“This is a devastating loss of life. Our thoughts are with the survivors and the families who have lost loved ones or remain without news of their relatives,” said Mr. Alexandre Coissac, IOM Chief of Mission in Djibouti. “Our teams are on the ground alongside local authorities to provide emergency assistance. This tragedy is a stark reminder of the dangers faced by migrants along this migration corridor as they seek economic opportunities.”
+The boat was travelling from Djibouti to Yemen when it capsized near Guhere, north of Obock, during the night of 8–9 October, according to survivors. Among the 109 bodies recovered are 52 men, 42 women and 15 children including nine girls and six boys. More than 80 people survived the shipwreck, all Ethiopian nationals. IOM is assisting 64 survivors at its Obock Migrant Response Centre (MRC), providing healthcare, psychosocial assistance, protection services, temporary shelter, food assistance, and support to restore contact with their families.
+Djiboutian authorities are continuing search and rescue operations as fears grow for those still missing. Local authorities are also providing medical care to survivors and arranging dignified burials for those who died.
+Each year, tens of thousands of migrants from the Horn of Africa travel through Djibouti and cross the Bab el-Mandeb Strait to Yemen, hoping to reach Gulf countries in search of safety, stability and employment. Poverty, insecurity and the growing impacts of climate change drive many to undertake this journey, despite mounting instability across the Middle East.
+Despite the violence in Yemen, migrants are still making the perilous journeys hoping to make it to the gulf countries. Since 10 September, more than 20,000 incoming movements to Djibouti from Ethiopia have been observed by IOM’s Displacement Tracking Matrix.
+The sea crossing is only one part of the danger. Migrants who reach Yemen face risks of violence, arbitrary arrest and detention, exploitation and trafficking. As movements along the Eastern Route continue, migrants remain exposed to severe risks at every stage of their journey, underscoring that surviving the sea crossing does not necessarily mean reaching safety, particularly amid the ongoing insecurity and humanitarian challenges in Yemen.
+In 2025, more than 900 migrants died or went missing along this route, according to IOM’s Missing Migrants Project, while the number undertaking the journey increased by 18 per cent. A further shipwreck in March 2026 left nine people dead and 45 missing.
+IOM works in close collaboration with Djiboutian authorities, to assist migrants and prevent deaths at sea and on land.
+With growing needs and limited funding, IOM urges donors and partners to strengthen support for Djibouti’s response, including search and rescue operations and life-saving assistance. It also calls for expanded safe migration pathways to reduce the risks faced by people undertaking these journeys.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:49:59.799990+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>IOM Chief Warns Smugglers Prey on Children as 20,800 of 31,100 Reached Europe Alone in 2025</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-chief-warns-smugglers-prey-children-20800-31100-reached-europe-alone-2025</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+07 October 2026
+Geneva, 7 October 2026 – More than 20,000 of the 31,100 children who reached Europe along mixed migration routes last year arrived without a parent or guardian, new UN data show. International Organization for Migration (IOM) Director General Amy Pope urged closer cooperation between European States and countries along the routes to protect children travelling alone and to counter the smuggling and criminal networks that prey on them.
+The findings suggest that reduced opportunities for safe, protection-sensitive movement along these routes may be pushing young people towards riskier journeys, with greater reliance on smugglers and greater exposure to violence, exploitation and abuse.
+“Children are making difficult and dangerous journeys without a parent or guardian by their side,” said Amy Pope, IOM Director General. “This report shows how exposed they are to violence and exploitation when safe pathways are limited, and they have to rely on smugglers. No child should have to face these risks alone. Our shared responsibility is to work across borders to protect them, uphold their rights, and provide the care and support they need.”
+Overall child arrivals by sea and land in Bulgaria, Cyprus, Greece, Italy, Malta and Spain fell by 25 per cent compared with 2024. Of the children who arrived, 78 per cent were boys and 22 per cent were girls. But the share recorded as unaccompanied rose to 67 per cent, up from 51 per cent a year earlier. The highest proportions were in Italy and Spain, where 86 per cent of children arrived alone.
+Italy ran against the downward trend. Overall arrivals there were stable, yet the number of children rose by 12 per cent to almost 14,100, most of them from Egypt, Eritrea, Somalia, Bangladesh and Ethiopia.
+The journeys are dangerous. IOM interviewed more than 4,600 adolescents and young adults aged 15 to 24 along the Mediterranean, Western African Atlantic and Western Balkan routes. Nearly half of those asked about their experiences reported physical violence. On the Central Mediterranean route, 28 per cent said they had been held against their will, and 17 per cent said they had been forced to work. Libya remained the country most often cited as the place where abuse occurred.
+Meanwhile, safe alternatives narrowed. Children made up half of the 6,800 people in refugee resettlement procedures to Europe in 2025: 3,400 children, compared with 8,900 a year earlier. Separately, only 199 children were relocated between European States under the Voluntary Solidarity Mechanism, down 67 per cent, and none of them was unaccompanied.
+In total, 214,600 children sought international protection in Europe in 2025, 79 per cent of them first-time applicants. Around 71 per cent of first-time applications were lodged in just four countries: Germany (30 per cent), France (19 per cent), Spain (15 per cent) and Greece (7 per cent). Of 210,900 first-instance decisions on children's claims, 56 per cent were positive, while rejections rose by 25 per cent.
+IOM urges European Union Member States to put the best interests of the child at the centre of every decision, to guarantee timely access to services, and never to detain children for immigration purposes. Unaccompanied and separated children should have immediate access to legal representation. Age assessments should be rare, child-sensitive and open to appeal.
+The report, Migrant and Refugee Children via Mixed Migration Routes in Europe: Accompanied, Unaccompanied and Separated – Overview of Trends 2025, is jointly produced by UNHCR, the UN Refugee Agency, UNICEF and IOM. It provides detailed statistics and analysis on accompanied, unaccompanied and separated children arriving in Bulgaria, Cyprus, Greece, Italy, Malta and Spain via sea and land mixed migration routes, and is available here.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:06.875825+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Nearly 2 Million in Gaza Need Urgent Shelter Assistance as Winter Looms: IOM Chief Warns</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/nearly-2-million-gaza-need-urgent-shelter-assistance-winter-looms-iom-chief-warns</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 9 October 2026 - Nearly all of Gaza’s population, almost two million people, still require shelter assistance one year after a ceasefire was announced. As winter rain begins, the combined supply pipeline of humanitarian shelter partners covers barely 17 per cent of identified winter needs, the International Organization for Migration (IOM) Director General Amy Pope warned today. 
+After years of displacement and widespread destruction, Palestinians are facing a fourth winter without adequate protection from rain, flooding and cold. Insufficient funding and continuing Israeli authorities' constraints on the entry of critical shelter supplies are preventing humanitarian organizations from responding at the scale required. 
+"Families who have already endured repeated displacement and devastating loss must be able to face the winter in safety and dignity," Pope said. "Shelter materials must enter quickly, predictably and at the scale required." 
+More than half of all tents and makeshift shelters currently in use are in poor condition that requires replacement. Tents are designed as a temporary emergency measure and generally last only six to 12 months. 
+With few alternatives available, many families are living in war-damaged buildings that pose serious risks to life. Just last month, dozens were killed in Gaza city when a war-damaged building collapsed. More than 3,600 structures were identified by an IOM partner in August as dangerous and at risk of collapse. The strengthening El Niño phenomenon is expected to bring heavier rainfall, which could further weaken unsafe buildings, while heavily damaged drainage systems leave communities exposed to flooding. 
+IOM and partners working in site management have identified nearly 1.8 million people living in displacement sites, most of them in areas at risk of flooding. Floodwaters could damage shelters, destroy families’ remaining possessions and force people to move once again.  
+Approximately 8,600 IOM emergency shelter kits are pre-positioned outside Gaza and ready for delivery but continue to be turned away at crossing points by the Israeli authorities. Meanwhile, humanitarian teams are using locally available and salvaged materials wherever possible. These efforts provide limited temporary support but are insufficient to meet widespread shelter needs.
+“The solutions are known, the supplies are ready and humanitarian teams are prepared to deliver,” Pope said. “Immediate and sustained humanitarian access is essential to protect lives, strengthen damaged shelters, and help families move beyond temporary solutions. All parties must facilitate principled humanitarian action and support a response equal to the severity of the crisis.”
+IOM calls for the immediate and sustained entry of tents, emergency shelter kits, relief housing units, wood, tools and other materials needed to reinforce shelters, repair damaged homes and support families seeking safer accommodation. Predictable access to specialized equipment, fuel, spare parts and construction materials will also be essential for debris removal and movement toward early recovery. 
+For more information, please visit IOM's Media Centre.  
+Notes to Editors
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:13.743759+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>New Global Migration Dataset Offers Unprecedented View of Mobility Trends</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/new-global-migration-dataset-offers-unprecedented-view-mobility-trends</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Berlin, 7 October 2026 – Policymakers and researchers seeking to understand how migration is changing globally have long faced a fundamental challenge: while data showing where migrants live are available for over half a century, there has been no comprehensive record of how migration movements between countries have evolved year by year over this period.
+The challenge is becoming increasingly urgent as countries respond to demographic change, labour shortages, displacement and other forces shaping human mobility. To help address it, the International Organization for Migration (IOM), with support from the German Government and research partners, has published FLOW, the first global dataset providing annual estimates of migration movements between all countries in the world since 1960.
+“Good migration policy starts with good data,” said IOM Director General Amy Pope. “By showing how migration has changed over time, FLOW can help us plan ahead and shape policies that better respond to the needs of migrants and communities.”
+Published in Nature Scientific Data, the open-access resource provides the most comprehensive historical picture to date of international migration patterns across more than six decades. The launch coincides with Director General Pope's visit to Berlin for High-Level Consultations with the Government of Germany and reflects a shared commitment to enhancing data and insights for migration governance.
+“This global new dataset demonstrates the value of cooperation between Germany and IOM,” said Niels Annen, State Secretary at Germany's Federal Ministry for Economic Cooperation and Development (BMZ). “It helps us see the long history of global migration more clearly, and enables deeper analysis to inform more impactful policies and programmes in countries of origin and destination.”
+The dataset provides annual, sex-disaggregated estimates of migration flows between all countries from 1960 onward, significantly expanding previous efforts by offering both global coverage and year-by-year estimates over a 65-year period. It offers a new resource for understanding how migration systems have evolved and how they may change in the future.
+To develop FLOW, researchers combined international migrant stock data from the United Nations and the World Bank with demographic information and observed migration flows. Using statistical modelling and machine-learning approaches, they reconstructed annual migration movements that can be compared consistently across countries and over time.
+“Estimating historical migration flows is challenging because each data source only provides part of the picture,” said Dr. Robert Beyer, data scientist at the IOM Global Data Institute and lead author of the study. “While uncertainties are unavoidable, the approach aims to extract as much information as possible from the available evidence to build a consistent picture of international migration over time.”
+The dataset is expected to support research, migration forecasting, demographic and labour market analysis, and policymaking, especially in countries where direct migration records remain limited or unavailable. The FLOW dataset and accompanying methodology are publicly available through Nature Scientific Data. 
+For more information, please visit IOM’s Media Centre. 
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:20.560100+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Yemen Displacement Tops 200,000, Needs Soar and Funding Alarmingly Dries Up</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/yemen-displacement-tops-200000-needs-soar-and-funding-alarmingly-dries</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Aden, 7 October 2026 – A total of 201,217 people have been forced from their homes in Yemen since fighting started, according to the latest data released today by the International Organization for Migration (IOM). The number is rising every day, and so are humanitarian needs. The money to help those in most need is alarmingly running out.
+"People are running for their lives and finding nowhere safe to go," said IOM Director General Amy Pope. "They need a roof, food and safety today. Our teams are on the ground, but the funding is not. I am asking donors to act now, because every day of delay costs lives. Yemen must not become a forgotten crisis. The world has the means to help. It must use them now."
+The speed of this crisis is alarming. In mid-September, IOM's Displacement Tracking Matrix (DTM) counted 76,000 displaced people. By the end of the month, the figure had passed 145,000. Today it stands at 201,217 people, or 33,776 households. Nearly all of them, 197,755, have fled since 1 September.
+Displacement now spans 10 governorates. Ta'iz is the hardest hit, with 114,708 displaced people, 57 per cent of the total. Lahj follows with 42,264, Aden with 20,814, Abyan with 9,030 and Al Hodeidah with 8,244. Smaller numbers are recorded in Hadramawt (2,478), Shabwah (1,188), Ma'rib (1,080), Al Maharah (936) and Ad Dali' (475).
+Three districts account for three in four of those recorded in Ta'iz: Al Ma'afer (31,230), Jabal Habashi (31,020) and Ash Shamayatayn (24,894). In Lahj, IOM recorded 23,616 people in Al Madaribah Wa Al Aarah and 14,676 in Tuban. In Aden, 10,320 were recorded in Al Burayqah. The crisis is also crossing borders.
+More than 3,700 people have fled by sea to Djibouti. They arrive exhausted, in overcrowded boats, with little food or water. Families are leaving with almost nothing. Many flee at night, carrying what they can. Most are women and children.
+For many, this is not the first time. Yemen has endured more than 12 years of conflict. Families who rebuilt their lives once, or twice, have lost everything again.
+IOM teams speak to displaced families every day. What they hear is clear. Shelter is the most urgent need, cited by 35 per cent. Food follows at 33 per cent. Cash support comes next at 22 per cent. One in ten say protection is what they need most.
+These are the basics of survival. Families are crowding into makeshift shelters or staying with relatives and neighbours. Host communities are sharing what little they have. They cannot carry this alone.
+"Every day our teams meet families who have lost everything," Pope said. "We know what they need. We know how to deliver it. What we lack is the means to reach them all."
+The response is badly underfunded. Yemen's humanitarian response plan is only 20 per cent funded. Relief stocks are running low. Needs are growing far faster than the resources to meet them.
+IOM teams are working with local authorities and partners to deliver emergency shelter, essential household items, cash, clean water and protection services. In Djibouti, IOM is helping people as they come ashore. It is not enough.
+IOM calls on the international community for immediate funding so humanitarian partners can save lives in Yemen. IOM also calls on all parties to protect civilians and aid workers, and to allow safe, unhindered access to people in need.
+Displacement is expected to keep rising in the coming days. IOM will continue to track movements and share verified data. A detailed data breakdown will follow.
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:28.915896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>New IOM Data: Yemen Displacement Reaches 184,000</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/new-iom-data-yemen-displacement-reaches-184000</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Aden, 5 October 2026 - Intense fighting in Yemen has displaced more than 184,000 people between 1 August and 4 October alone, the majority since the start of September, according to IOM's Displacement Tracking Matrix (DTM).
+In the week between 27 September and 3 October, DTM recorded 21,798 individuals, or 3,633 households, who were displaced at least once, representing a 26 per cent increase on the previous week. A further 6,474 people, or 1,079 households, were displaced on 4 October alone. All are in need of food, shelter, and other basic humanitarian assistance.
+"As the conflict intensifies, more and more people are thrown into an appalling cycle of displacement, living in fear of their lives and with their futures uncertain," said IOM Director General, Amy Pope. "We reiterate the urgent need for securing humanitarian access to all those impacted. The international community must urgently do more to allow humanitarians to meet critical needs."
+A rapid protection assessment conducted in three displacement sites in Ma'rib last week found that the lack of safe shelter remains the most critical vulnerability factor. Some assessed households are sleeping in the open, which exposes them to violence and to the effects of the conflict, such as airstrikes. Women and girls raised the shortage of appropriate latrines as a concern.
+Approximately 45 per cent of assessed households had experienced displacement before, together with loss of assets and unstable livelihoods, reducing households' ability to cope. In these conditions, households may turn to harmful coping strategies including child labour, IOM warns.
+The assessment also identified multiple and intersecting vulnerabilities among persons and households, including persons with disabilities, female-headed households, children and older persons.
+IOM teams are working with local authorities and humanitarian partners to reach newly displaced families with emergency shelter, essential household items, cash assistance, clean water and sanitation, and protection services. DTM monitors population movements every day, and its data helps partners deliver aid where it is needed most.
+IOM calls for the protection of civilians and humanitarian workers, and for safe, unimpeded access so that aid can reach displaced families and the communities hosting them.
+With the situation remaining volatile, further displacement is possible in the coming days. IOM will continue tracking population movements and sharing verified data as events unfold. 
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:37.028632+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Over 145k Now Displaced in Yemen, 16,000 Increase in Past Week</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/over-145k-now-displaced-yemen-16000-increase-past-week</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Aden, 28 September 2026 – More than 145,000 people have been displaced across eight governorates in Yemen since conflict escalated on the West Coast in June, according to new figures released today by the International Organization for Migration (IOM). As of today, the total stands at 145,308 people, or 24,218 households, a rise of 15,870 compared with 21 September and an increase of more than 12 per cent in one week. Insecurity continues to uproot families along the West Coast and across the south.
+"Every week we count thousands more people who have left everything behind," said Abdusattor Esoev, IOM Yemen Chief of Mission. "Behind these figures are parents trying to keep their children safe, older people who cannot travel far, and families who had very little to begin with. They need help now, and our response has to move as fast as they are."
+Ta'iz Governorate remains at the centre of the crisis, hosting the largest number of displaced people with 81,444, more than half of the national total. That is nearly 8,000 above the figure recorded a week ago. Lahj now hosts 34,860 people, followed by Aden with 12,456, Al Hodeidah with 8,244, Abyan with 5,568, Hadramawt with 1,974, Ma'rib with 750 and Al Maharah with 12, who were displaced earlier this month.
+Outside Ta'iz, Aden recorded the largest increase. The number of displaced people there rose by nearly 40 per cent in a single week, an increase of 3,510. Al Burayqah district alone now hosts close to 6,500 people. More families are heading to urban areas, placing further strain on housing, services and livelihoods that were already stretched. Numbers are also climbing quickly further east: displacement nearly doubled in Hadramawt and rose by two-thirds in Abyan over the same period.
+IOM teams are working with local authorities and humanitarian partners to reach newly displaced families with emergency shelter, essential household items, cash assistance, clean water and sanitation, and protection services. IOM's Displacement Tracking Matrix monitors population movements every day, and its data help partners send aid where it is needed most.
+IOM calls for the protection of civilians and humanitarian workers, and for safe, unimpeded access so that aid can reach displaced families and the communities hosting them.
+"Communities in Ta'iz, Lahj and Aden have opened their doors to people fleeing the fighting, but goodwill alone cannot cover what is needed," said Esoev. "Families urgently need shelter, food and protection, and the towns receiving them need help to cope. Needs are growing faster than our resources, and more support is needed now to keep pace."
+With the situation remaining volatile, further displacement is possible in the coming days. IOM will continue tracking population movements and sharing verified data as events unfold.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:43.854044+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>New IOM Data: Nearly 1.5 Million Displaced in Haiti as Hurricane Risks Mount</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/new-iom-data-nearly-15-million-displaced-haiti-hurricane-risks-mount</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Port-au-Prince/Geneva, 25 September 2026 – New data from the International Organization for Migration (IOM) released this week show that Haiti's displacement crisis is spreading beyond the capital, with some of the country's sharpest increases now occurring in regions that were once considered relatively safer.
+The latest assessment identified nearly 1.5 million internally displaced people across the country and points to a significant shift in where displacement is concentrated: nearly 80 per cent are now located outside Port-au-Prince, as violence continues to spread into other parts of Haiti.
+"What we are witnessing in Haiti is not a crisis that moves from emergency to recovery. Violence, displacement, food insecurity, forced returns and climate risks are all unfolding at the same time, placing enormous pressure on families and communities," said Elise Verron, Senior Emergency Coordinator with IOM Haiti. "The displacement trends show that this crisis is expanding geographically. Communities that were already struggling to meet their own needs are now carrying an even greater burden."
+The most significant increase was recorded in the Artibonite department between May and August 2026 where displacement rose by 16 per cent over the past three months. Once considered a refuge for families fleeing violence elsewhere, parts of Artibonite are now experiencing escalating insecurity, forcing new waves of displacement and further reducing safe options for affected populations.
+Recent violence in Kenscoff, near the capital, also underscores the continued volatility of the situation. Armed attacks displaced more than 4,000 persons, with reports of homes burned, kidnappings and loss of life. Most of those affected have sought refuge with host families or across six displacement sites in neighbouring areas of Port-au-Prince.
+The worsening displacement situation comes as Haiti remains exposed to hurricanes, tropical storms, flooding and landslides during the Atlantic hurricane season. Hundreds of thousands of displaced persons are currently living in host communities, informal settlements, collective sites or other precarious conditions, increasing their vulnerability to extreme weather events.
+"For families already displaced by violence, a major storm could trigger another humanitarian emergency," said Verron. "Many households have few resources to withstand additional shocks, and communities hosting displaced families are already under considerable strain."
+The assessment also highlights mounting pressures in border departments, where local authorities and host communities are responding simultaneously to internal displacement and the arrival of Haitians returned from neighbouring countries. This convergence of needs is placing additional strain on housing, health services, water systems and other essential resources.
+Although returns have increased in some areas, many families continue to face difficult conditions, with insecurity, limited livelihood opportunities and inadequate access to basic services limiting prospects for sustainable recovery.
+Under its crisis response plan, IOM is appealing for USD 60 million to reach 6.4 million people. The Organization is calling for sustained investment to provide life-saving assistance and support recovery, strengthen local systems and help communities withstand the combined impacts of insecurity, displacement and climate-related shocks.
+For more information, please contact IOM Media Centre
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:50:59.291761+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>KSrelief and IOM Join Forces to Provide Safer Shelter and Vital Aid Amid Escalating Crisis</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/ksrelief-and-iom-join-forces-provide-safer-shelter-and-vital-aid-amid-escalating-crisis</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+New York, 24 September 2026 – The King Salman Humanitarian Aid and Relief Centre (KSrelief) and the International Organization for Migration (IOM) have signed a USD 2.6 million agreement to improve living conditions for internally displaced people and vulnerable host communities in Yemen.
+The signing took place on the sidelines of the 81st session of the United Nations General Assembly in New York.
+"Families displaced by conflict in Yemen need a safe place to live, with privacy and protection from harsh weather. As renewed fighting forces more people from their homes, those needs are becoming more urgent. Our partnership with KSrelief will help families find safer shelter and regain some stability in their daily lives,” said Amy Pope, IOM Director General.
+The agreement comes amid a sharp escalation in hostilities in Yemen that has driven new displacement and deepened humanitarian needs. In 2026, 22.3 million people – more than two thirds of the population – require humanitarian assistance and protection, while recent hostilities have displaced more than 134,000 people since early September.
+Years of conflict and economic deterioration have already forced more than five million people to leave their homes, leaving many in inadequate shelter conditions and increasingly exposed to environmental hazards that continue to damage shelters and essential infrastructure.
+Over the next 18 months, the project will directly support 1,900 crisis-affected families in Ma'rib, Ta’iz and Hodeidah with transitional shelters, essential household items and emergency shelter solutions, including safer, more durable shelter solutions designed to better withstand recurrent flooding, extreme weather and other hazards.
+The intervention will help reduce overcrowding and protection risks, while improving privacy, safety and dignity for displaced families and host communities, with particular attention to women, girls, older people, persons with disabilities and female-headed households.
+IOM will implement the project in coordination with local authorities and humanitarian partners, prioritizing households with the greatest needs and engaging affected communities throughout implementation.
+IOM’s partnership with the Kingdom of Saudi Arabia has contributed over USD 140 million in humanitarian and recovery programming across multiple crises. In Yemen, this support has helped expand access to water and sanitation services, strengthen protection assistance, rehabilitate necessary infrastructure, and provide emergency shelter and essential non-food items for crisis-affected and displaced communities.
+For more information, please visit IOM’s Media Centre.     
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:06.154500+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Five Influential Voices from Sport, Culture and Public Life Join IOM as Goodwill Ambassadors</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/five-influential-voices-sport-culture-and-public-life-join-iom-goodwill-ambassadors</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 24 September 2026 – The United Nations’ International Organization for Migration (IOM) has appointed five new Regional and National Goodwill Ambassadors from the worlds of sport, music, entertainment, fashion and public life to help advance understanding, inclusion and opportunities for migrants and displaced people worldwide. At a time of record displacement, rising global mobility and escalating humanitarian crises, migration and displacement continue to shape communities across the globe. Yet public discussions are increasingly polarized, often overlooking the experiences, contributions and aspirations of the people affected.
+The new ambassadors are Pritika Swarup (Regional Goodwill Ambassador for North America), American international fashion model and entrepreneur;  Luiza Brunet (National Goodwill Ambassador for Brazil) Brazilian model and longtime advocate for women's rights; Fatoumata Diawara (National Goodwill Ambassador for Mali), internationally acclaimed Malian singer-songwriter and actress;  Deo Kato (National Goodwill Ambassador for the United Kingdom), British-Ugandan endurance runner and activist known for his 13,000-kilometre run from Cape Town to London; and Nicolas Brice Moumi Ngamaleu (National Goodwill Ambassador for Cameroon), Cameroonian international footballer.
+Representing diverse regions, cultures and professional backgrounds, they will help IOM engage audiences where they have particular cultural relevance, influence and reach, including diaspora communities and audiences beyond their countries and regions. Through their platforms, they will foster greater understanding of migration and displacement, amplify the voices of migrants and displaced people, and encourage solidarity with affected communities.
+"As the world faces multiple, overlapping crises, it has never been more important to build understanding and bring people together," said Stephanie Dei, Director of IOM’s Private Sector Partnerships Division. "These ambassadors have the ability to reach audiences across generations and communities. Their voices can help challenge misconceptions, promote inclusion and inspire support for a future where migrants and displaced people can live in safety, dignity and hope."
+For more than 75 years, IOM has worked alongside governments, communities and partners to support migrants and displaced people, respond to humanitarian emergencies, strengthen migration governance and help people build better futures. Migration, when safe and well-governed, is also a powerful driver of development, contributing skills, remittances and innovation to both countries of origin and destination. Today, IOM works in more than 170 countries, supporting people affected by conflict, disasters, climate change and other drivers of migration and displacement.
+Goodwill Ambassadors play an important role in connecting global audiences with these realities. Through their visibility and influence, they help bring attention to issues that often compete with multiple global crises for public awareness, and by sharing stories of resilience, contribution and human potential, they help counter stigma and strengthen social cohesion.
+Over the coming year, the ambassadors will take part in campaigns, events and storytelling initiatives designed to engage audiences across regions and generations, with the idea to reinforce a simple message: behind every journey is a person with aspirations, talents and potential. 
+Learn more about IOM’s Goodwill Ambassadors here. 
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:14.373513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>IOM Chief Calls for Urgent Support as DRC Faces Largest Ebola Outbreak on Record</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-chief-calls-urgent-support-drc-faces-largest-ebola-outbreak-record</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Nairobi, 22 September 2026 – As the Ebola outbreak in the Democratic Republic of the Congo (DRC) reaches unprecedented levels, the International Organization for Migration (IOM) is expanding efforts to strengthen disease surveillance and preparedness along major travel routes including riverine corridors and across borders to help prevent further spread.
+Since the outbreak was declared in May 2026, the numbers have continued to climb. More than 7,400 confirmed cases have now been recorded, making this the largest Ebola outbreak ever reported in the country, and a crisis exacerbated by ongoing conflict and large-scale displacement. As of 16 September, the World Health Organization had reported over 3,600 deaths. Over the same period, IOM has supported local authorities with over 33 million health screenings across the region, reaching millions of people with life-saving information and referrals to appropriate services.
+“This is the largest Ebola outbreak the DRC has faced, putting families affected by conflict and crisis under even greater strain. Our teams are working alongside local health authorities to detect risks early and help people access care. Close cooperation across borders is vital to containing the disease,” said Amy Pope, IOM Director General. "But we have received less than a third of the funding needed for our response. We urgently need more support to sustain this work and protect communities in the DRC and neighboring countries.”
+Displaced people, and host communities within the outbreak epicentre face particular barriers to accessing health services. Overcrowding, inadequate water and sanitation services, limited access to lifesaving services, and gaps in disease surveillance in displacement sites make early detection more difficult.
+IOM is strengthening disease surveillance and preparedness across DRC using population mobility mapping and flow monitoring to identify high-risk mobility corridor, border communities points of entry (PoEs) and informal crossing points, enabling authorities to better target the response to a fast-moving disease.
+The organization is also scaling up disease surveillance at displacement sites and along the Congo River, a key route for people travelling towards Kinshasa. At the Bende-Bende point of control, IOM is supporting health authorities with training and other critical preparedness activities alongside traveller screening, with teams conducting an average of around 1,000 health screenings a day.
+IOM is working closely with governments and partners in neighbouring countries, including Uganda, South Sudan Burundi, Rwanda, Central African Republic along with other at-risk countries across the region, to strengthen preparedness and reduce the risk of cross-border transmission.
+To sustain and expand this work, IOM is seeking USD 110 million for its multi-country Ebola Virus Disease Preparedness and Response Plan. So far, USD 29.6 million has been received, leaving more than half of the appeal unfunded. Additional resources are urgently needed to sustain surveillance along key movement routes, strengthen preparedness in neighbouring countries, and ensure mobile and displaced communities are included in the response.
+IOM's response is supported by the United States Government, the United Nations Central Emergency Response Fund (CERF), European Union, the Government of Japan and the World Bank.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:21.176210+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>New IOM Data: Nearly 130,000 Displaced in Yemen Due to Escalating Conflict</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/new-iom-data-nearly-130000-displaced-yemen-due-escalating-conflict</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+21 September 2026
+Geneva/Aden, 21 September 2026 – The latest data from the International Organization for Migration (IOM) show that 129,438 people, or 21,573 households, have been displaced across seven governorates in Yemen as families flee escalating insecurity.
+"Nearly 130,000 people have been forced from their homes in just a few weeks. Many have already moved more than once to find safety," said Othman Belbeisi, IOM Regional Director for the Middle East and North Africa. “The numbers keep climbing. On 18 September we recorded 118,086 displaced people. Three days later, the figure has risen by 11,352”.
+Today's update from IOM's Displacement Tracking Matrix (DTM) shows that Ta'iz Governorate hosts the most displaced people, with 73,494. Lahj follows with 33,828, then Aden with 8,946 and Al Hodeidah with 8,244. Abyan (3,324), Hadramawt (1,008) and Ma'rib (594) have also received new arrivals.
+Jabal Habashi in Ta'iz is hosting the highest number of displaced people, with over 23,000 recorded. Meanwhile Al Madaribah Wa Al Aarah in Lahj hosts nearly 21,500, Al Ma'afer in Ta'iz has more than 16,500, and over 12,300 people have sought safety in Ash Shamayatayn.”
+“These are families who have lost their homes and their income,” said Belbeisi. “They are arriving in towns that were already struggling. Host communities are sharing the little they have, but they cannot do it alone. We need support now, for the people who have fled and for those who are taking them in."
+Meanwhile, as of yesterday evening of 20 September, 3,106 had crossed the Red Sea from Yemen to Djibouti. IOM is providing urgent assistance to many of them and is appealing for greater support.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:28.197186+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>5 Million Sudanese Return Home to Broken Places, IOM Warns</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/5-million-sudanese-return-home-broken-places-iom-warns</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 21 September 2026 – More than 5.1 million people have returned to their areas of origin in Sudan, while 8.6 million remain displaced, the International Organization for Migration (IOM) said today. Many are going back to a country still wracked by conflict, where damaged homes, schools and clinics cannot meet the needs. Without urgent support, families risk being uprooted again.
+New data from IOM's Displacement Tracking Matrix (DTM) records 5,145,165 returnees in 76 localities across nine states: four per cent more than last month. Another 8,583,274 people are still displaced in 185 localities across all 18 states. This is about one per cent lower than last month and 26 per cent below the peak of the crisis. Even with these new figures, Sudan still hosts one of the largest displaced populations in the world.
+"More than five million Sudanese have gone home. That says a lot about their courage and their hope," said IOM Director General Amy Pope. "But getting home is only the start. Many families are returning to homes that are damaged, schools that are closed and clinics that barely function. There are few livelihood opportunities. If we don't help them now, many will be forced to move again. We need to invest in these communities today, so people can rebuild their lives and stay."
+Most returnees, 82 per cent or roughly 4.2 million people, had been displaced inside Sudan. The other 18 per cent, roughly 930,000 people, came back from abroad. Among those returning from abroad, Egypt was the primary country of return (50%), followed by South Sudan (25%), Libya (10%) and Gulf countries (8%).
+IOM is calling on governments, donors, development partners, international financial institutions and humanitarian organizations to act now. Humanitarian assistance must continue for displaced people and vulnerable returnees, IOM warns. Long-term investment is just as urgent. Basic services must be strengthened, infrastructure restored and livelihoods supported, so that people can remain safely where they return and host communities hosting both returnees and displaced populations can withstand further shocks.
+While the number of displaced people has declined from its peak, more than 8.5 million people remain uprooted across Sudan, with new displacement continuing in parts of Darfur, Kordofan and Blue Nile due to ongoing insecurity. Sustained investment in life-saving assistance, particularly shelter, non-food items, protection and basic services, remains essential alongside support for returns and recovery.
+About half of displaced people and 50 per cent of returnees are under 18. Millions face interrupted schooling, limited health care and gaps in protection. Giving them access to basic services and opportunities will be critical to Sudan's long-term recovery and stability.
+For many returnees, coming home does not mean recovery. Damaged infrastructure, fragile local economies and few livelihood opportunities are putting extreme pressure on returnees and on the communities hosting them, particularly acute in high-return areas, where public services and local infrastructure remain stretched to breaking point.
+The five million milestone is a rare sign of progress in a prolonged humanitarian crisis, but it is fragile. What the international community does now will determine whether Sudan can move from displacement to recovery, or whether hard-won gains are reversed. 
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:35.473912+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Criminal Networks Work Across Borders. So Must States, IOM Chief Tells UN</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/criminal-networks-work-across-borders-so-must-states-iom-chief-tells-un</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+New York / Geneva, 21 September 2026 – Smugglers and criminal networks operate across borders, exploiting gaps. Governments must respond the same way with solutions across the routes people travel. That is the message IOM Director General Amy Pope is bringing to the UN General Assembly this week.
+The International Organization for Migration (IOM) is calling on states to address shared challenges and opportunities across entire migration routes, from where they leave to where they arrive. The aim is solutions that work for everyone.
+"Smugglers don't see borders. They see a route, and they run it like a business. They plan ahead, and they move to exploit gaps between countries." said DG Pope. "When countries work together, they can save lives, disrupt criminal networks, and manage their borders more effectively. That is one of the main topics we are putting on the table this week."
+This is in line with the Route-Based Approach, which involves identifying the challenges along key migration routes and making sure partners work together to address them effectively - from tackling root causes of irregular migration to disrupting smuggling networks to ensuring migrants' rights are protected along the whole route. Countries plan together and act at the same time. Each government retains full control of its own borders and laws, while sharing information, coordinating actions, and closing the gaps criminal networks seek to exploit.
+War, climate shocks and economic hardship are forcing millions of people from their homes. More than 83 million were living in internal displacement at the end of 2024, according to IOM's World Migration Report 2026. Many others cross several countries on one journey, and smugglers and traffickers exploit them along the way. Smuggling and trafficking are both billion-dollar businesses, and people pay with their lives.
+Nearly 8,000 people died or went missing on migration routes worldwide in 2025, according to IOM data. As of 15 September, arrivals in Europe by sea this year are down 39 per cent, yet at least 2,292 people have died or gone missing on the way, up from 1,999 at the same point last year. In July, IOM warned that hundreds of thousands of people have been trafficked and forced to run online scams.
+IOM is calling on governments at the Assembly to focus on three practical areas: share information along their routes; expand more legal ways to work and travel, so fewer people turn to smugglers; and invest in people at home, with jobs and help after climate shocks, so leaving is a choice, not the only option. Well-managed migration also builds public trust, because people can see order, fairness and results.
+Business has a role to play too. Companies create jobs, and legal jobs offer a safer alternative to abusive journeys. IOM is working through the UN Network on Migration and with private-sector partners, local communities and faith groups along the key migration routes.
+As Member States call for a UN that delivers more effectively, IOM continues to contribute to UN80, the UN's reform effort to reduce duplication and focus on results. IOM is sharing services, data and innovation with other UN agencies to deliver just that. More than 93 per cent of its operational budget goes directly to field projects.
+"Every dollar has to work. Governments are right to ask that, and we hold ourselves to the same standard," said DG Pope. "But efficiency is not the only goal. People are at heart of this, making sure the resources entrusted to us reach the people who need them most."
+This year also marks IOM's 75th anniversary and 10 years as part of the UN system. Over the past decade, IOM has helped an average of 29.3 million people a year in 170 countries, by responding to crises and supporting recovery.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:43.597605+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>New IOM Data: Migrant Arrivals to Europe Fall 39% in 2026 While Deaths Continue to Rise</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/new-iom-data-migrant-arrivals-europe-fall-39-2026-while-deaths-continue-rise</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+GENEVA, 17 September 2026 – Arrivals to Europe have fallen sharply this year but deaths along the Central Mediterranean routes keep climbing, according to new data from the International Organization for Migration (IOM).
+Nearly 60,000 migrants and refugees have arrived in Europe by sea so far in 2026. That's down 39 per cent from 98,040 during the same period last year. Yet, at least 2,292 people have died or gone missing attempting the crossing, up from 1,999 for the same period last year. The Mediterranean and Atlantic routes are the deadliest maritime routes in the world.
+"These figures tell two stories at once," said Amy Pope, IOM Director General. "Fewer people are arriving by sea in Europe than at this point last year. But people are still dying and going missing in alarming numbers trying to reach safety. Nearly every death and disappearance at sea is preventable. The consequences continue long after. Human remains go unidentified, leaving families searching across borders for answers, often for years."
+The steepest drop was on the Central Mediterranean route to Italy. Arrivals there fell 55 per cent, from 48,231 to 21,393. But deaths on that route rose too, from 844 to 996.
+Greece recorded 20,428 arrivals, down from 25,427. Deaths on the Eastern Mediterranean route jumped from 284 to 417. Spain saw 16,794 arrivals across the Atlantic and Western Mediterranean routes, down from 22,855. Fatalities there remained high, at 879.
+Interceptions continue at scale. Between January and mid-September, 17,067 migrants were intercepted at sea and returned to Libya, according to Libyan Coast Guard figures tracked by IOM.
+"Behind every number is a human being, a family, a community," Pope said. "Deaths rising even as arrivals fall shows migrants are taking increasingly dangerous journeys. We need sustained international cooperation that saves lives, protects people on the move, combats trafficking and exploitation, and expands safe, regular pathways." Sustained efforts are also needed to clarify the fate and whereabouts of missing migrants, and support affected families, in line with the Global Compact for Safe, Orderly and Regular Migration.
+IOM continues working with governments, partners and communities across countries of origin, transit and destination. The focus: stronger protection, voluntary return and reintegration support, expanded regular pathways, and reduced risk along major migration routes. Recent talks between IOM and European partners have underscored the need for a comprehensive, region-wide approach.
+The figures come from IOM's Displacement Tracking Matrix (DTM) and Missing Migrants Project, covering verified incidents and arrivals through 15 September 2026. Because many shipwrecks and disappearances go unrecorded, the true death toll is likely higher.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:50.509887+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Yemen Displaced Top 104,000 as IOM Calls for Urgent Action</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/yemen-displaced-top-104000-iom-calls-urgent-action</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 16 September 2026 – The number of people displaced inside Yemen has passed 104,796, across 17,461 households, according to the International Organization for Migration's (IOM) Displacement Tracking Matrix (DTM) released today. Fighting along the West Coast shows no sign of easing.
+In Djibouti, the number of people who have crossed from Yemen reached 2,776, according to latest data obtained. IOM continues to respond with immediate services, including 1500 hot meals, twice a day.
+"Yemen is a country torn by war, displacement, poverty, and climate impacts," said Amy Pope, IOM Director General. "Overlooking the suffering of civilians is not acceptable as needs continue to rise.”
+Aid workers say the pace of displacement is outstripping their ability to track it in real time. Families are moving under fire, often at night. Many carry little more than what they can hold.
+Taiz remains the epicentre, with over 63,000 people displaced across its districts, led by Jabal Habashi (21,018), Al Ma'afer (12,642) and Ash Shamayatayn (8,250). Lahj follows with nearly 26,400 displaced, driven largely by Al Madaribah Wa Al Aarah district, where almost 19,000 people have fled. Aden has recorded over 3,500 displaced, while Al Abyan, Hadramawt and Ma'rib are also seeing rising numbers as fighting spreads. In total, 104,796 people across 17,461 households have now been displaced.
+In response to escalating needs, IOM is assisting newly displaced families through Rapid Response Mechanism (RRM), Shelter and Non-Food Item (NFI), and protection assistance. IOM is also monitoring population movements through DTM, generating real-time data to support the country-wide response. IOM currently operates in Aden, Ma'rib, Lahj and South Taiz, with capacity to deploy teams to accessible areas as needed.
+Since the start of the conflict, IOM's RRM and Cash-Based Interventions (CBI) team has registered and assisted 1,159 households with in-kind assistance. Emergency Multi-Purpose Cash Assistance (MPCA) distributions are ongoing despite increasingly constrained access.
+On shelter, IOM is supporting 460 families with NFI assistance and 449 households with shelter support. As protection risks grow for the most vulnerable, including IDPs and migrants, IOM has provided protection services to 758 people in Ma'rib, Aden and Lahj.
+IOM also manages the WASH Cluster emergency pipeline, with approximately 8,000 pre-positioned WASH kits in Aden and Ma'rib, ready for deployment within 72 hours.
+IOM co-leads Yemen's Refugees and Migrants Multi-Sector (RMMS) response and the RRM at national level. It manages the Humanitarian Hub in Ma'rib, hosting eight UN agencies, and co-leads the Shelter, Land and Site Management Cluster and the WASH Cluster, serving as SLSC Area of Responsibility lead in Aden and co-chair of the Yemen Cash and Markets Working Group.
+IOM is calling on donors to act now to fund the response before more families are forced from their homes with nothing left to lose.
+The situation remains volatile, with further displacement expected in the coming days. IOM will continue to monitor developments and provide updates as they become available. 
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:51:58.732486+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Statement on Helping Third-Country Nationals</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/statement-helping-third-country-nationals</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 15 September 2026 — The International Organization for Migration (IOM)’s work in countries that receive third-country nationals — people who are removed from a country of residence to a country other than their own country of nationality — focuses on safeguarding the health, safety, dignity and well-being of the people impacted. Our support begins only after they arrive in a receiving country, only at the request of the receiving government, and only where essential safeguards are in place.
+The circumstances that send people to third countries are not new, and not confined to any one government. States in different regions have pursued or considered similar approaches for years, and IOM’s position is the same wherever these approaches arise. Migration policy, including decisions on removal, is the sovereign responsibility of states. Our support is part of our long history of providing essential assistance to migrants who find themselves stranded or in situations of extreme vulnerability — whether that vulnerability arises from conflict, disaster, or a government’s policy decision. This is central to our mandate: to assist people to meet their basic needs at the most vulnerable time of their lives. We have done this for adults and children who face all manner of challenges.
+The people IOM assists in the context of third-country removals receive basic services: health care, counselling, protection screening, and clear, accurate, neutral and complete information about the options available to them. Where someone asks us to help them return to their country of origin, or to another country where they have the legal right to stay, we do so only after individualized counselling and protection screening, and only where the decision is made freely, voluntarily and on the basis of informed consent.
+Most recently, public reporting indicates that since the beginning of 2025, tens of thousands of people have been removed from the United States to third countries. IOM’s engagement in this context depends entirely on being asked by the receiving government, and on safeguards being in place. Where we have been asked and those conditions exist, we have supported roughly 800 people, providing health care, counselling, and protection screening; about 300 later chose voluntary return. The gap between that number and the tens of thousands removed is not a measure of IOM’s effort — it reflects how few governments have invited us in or met the conditions we require. Most people removed have received no support of any kind.
+We are fully aware that states sometimes use international aid to advance their national priorities, and that funding for this work typically comes from the governments involved in the removals themselves. Accepting that funding does not mean accepting direction: IOM retains full control over how assistance is delivered, who delivers it, and on what terms, and we have walked away from funding where a government would not accept those terms. Every decision to engage rests on one question — whether our engagement will improve conditions for the people affected, measured against the realistic alternative of no assistance at all — not on the source of the funds. This is consistent with the humanitarian principles of impartiality and independence that govern all our work. Accepting funding to help people is not an endorsement of the policy that put them in need of help.
+Before IOM agrees to work in any country, we assess whether receiving governments are prepared to commit to putting essential safeguards in place, including legal stay arrangements, freedom of movement, and access to international protection. We assess risks precisely so we can decide whether those risks can be adequately addressed. Where those conditions could not be met, we have declined to engage, or we have put limits on what we do, irrespective of the funding and relationship consequences. Removals to these countries still take place without our engagement, but as a result migrants are more likely to be detained on arrival, or deported to their country of origin without the safeguards we would otherwise secure.  
+IOM does not engage in forced movements or detention anywhere. We play no role in any country’s decision to admit or remove people, and we do not determine migration policy for any country.
+Some argue that IOM’s engagement enables the policies of removal to third countries. It does not. Our engagement means that people who have already been removed are met with health care, counselling, and someone who can explain their options, instead of nothing. The people we assist tell us this themselves.
+The choice in front of us is not between removal and no removal — that decision has already been made by others before we are ever contacted. The choice is between a person facing that situation with health care, information, and a protection screening, or facing it with none of those things. We know which of those outcomes we would choose for someone we cared about.
+IOM stepping back would not stop these removals. And those who argue we should withhold basic assistance to make a policy point are asking IOM to ignore the ordeal faced by extremely vulnerable individuals. We will not do that. IOM will not leave people to face impossible circumstances alone. 
+For more information, please contact IOM Media Center.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:06.685771+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>IOM Spokesperson: Numbers of Displaced in Yemen Reaches Nearly 94,000</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-spokesperson-numbers-displaced-yemen-reaches-nearly-94000</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+14 September 2026
+Geneva, 14 September 2026 – The International Organization for Migration (IOM) reports that 93,864 individuals have been newly displaced across Yemen, driven by ongoing conflict.
+The heaviest impact is concentrated in Ta'iz and Lahj governorates. In Ta'iz's Jabal Habashy district alone, 18,840 people have been displaced, with a further 9,966 displaced from Al Ma'afer. In Lahj, Al-Mudharibah district accounts for 16,464 displaced, with Tuban adding another 2,892.
+Displacement has also been recorded across Aden, Al Hodeidah, Abyan and additional districts in Ta'iz, reflecting the widening geographic scope of the crisis.
+IOM and partners are responding on the ground and continue to monitor displacement trends. IOM is calling for urgent support to meet the shelter, water and sanitation needs of newly displaced families.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:15.008894+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Sudan Aid Could Collapse Within Weeks Amidst Conflict, Rising Needs: IOM Chief Warns</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/sudan-aid-could-collapse-within-weeks-amidst-conflict-rising-needs-iom-chief-warns</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Port Sudan/Geneva, 14 September 2026 – As hundreds of thousands of displaced people across Sudan continue to face severe shelter shortages and heightened risks from ongoing fighting and heavy rains, the International Organization for Migration (IOM) is warning of an imminent end to Sudan’s emergency relief supply via the IOM Common Humanitarian Pipeline.  
+"We simply can't turn our back on the people of Sudan when they need us most amid raging conflict, increased displacement and the impact of heavy rain," said Amy Pope, IOM Director General. "The entire humanitarian system could collapse within weeks if we don't act now. Without new funding, we won't be able to get help where it's needed most."
+IOM’s warning comes as needs remain acute amid heightened displacement in conflict and crisis-affected communities across Sudan, leaving vulnerable families exposed and the humanitarian system on the edge of collapse. To date, 8.6 million people remain internally displaced and 4.9 million returnees have been recorded by IOM's Displacement Tracking Matrix. Nearly 70 per cent of internally displaced people are living with host families or in informal settlements. Ongoing violence, floods and heavy rains continue to damage shelters forcing people to move.
+Managed by IOM, the Common Humanitarian Pipeline system has reached 2.84 million people since July 2023. Yet its reach is shrinking even as needs remain all-time high: more than 1 million people were assisted through the Pipeline in 2024, falling to 804,000 in 2025, while so far in 2026, IOM has provided shelter and emergency support kits to 330,000 people. 
+Without immediate donor support, current shelter, sanitation and emergency household relief items are expected to be depleted by the end of September 2026. The warehousing and operational capacity that keeps the Pipeline functioning can only be sustained until December 2026. 
+As a shared logistics system for the UN and its partners and one of the key enablers of the humanitarian response in Sudan, the Common Pipeline enables timely, coordinated and efficient dispatch of emergency relief items to people in need. The disruption of the Pipeline would significantly weaken the humanitarian community’s ability to rapidly deliver and mobilise lifesaving-assistance through a network of more than 100 registered partners. Rebuilding the system after any interruption would be a complex, costly and time-consuming process, requiring substantive resources to reestablish supply chains, operational systems and partner coordination networks. 
+IOM requires USD 15 million to maintain the Common Pipeline at its 2026 minimum capacity for 12 months, supporting 305,000 people. USD 27 million would restore assistance to approximately 2025 levels and reach 570,000 people, while USD 42 million would enable a scale-up to provide immediate lifesaving support for up to one million people. 
+For displaced families, inadequate shelter carries wider risks. Prolonged exposure to weather, disease and insecurity can heighten risks of gender-based violence, family separation and eviction in overcrowded sites. Continued underfunding also raises the risk of shelter failure and flood-related secondary displacement in sites already at or beyond capacity.  
+With relief item stocks expected to run out by the end of September and operational capacity at risk thereafter, funding will now determine whether this established emergency supply mechanism remains ready to respond amid ongoing conflict-related displacement and the current rainy season.  
+For more information, please contact IOM Media Center.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:23.224647+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Yemen Displacement Tops 85,000 as Conflict Continues, 2,000 Flee to Djibouti</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/yemen-displacement-tops-85000-conflict-continues-2000-flee-djibouti</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 13 September 2026 – According to the International Organization for Migration's (IOM) Displacement Tracking Matrix (DTM), displacement in Yemen, the Arab world's poorest country, has now reached 85,818 people, up sharply in recent days (82,164 since beginning of September alone ) as fighting continues along the West Coast. Families are being forced from their homes, and some are now fleeing the country altogether.
+Over 2,000 people fleeing the hostilities have reached Djibouti's northern shores so far, landing at scattered points along the coast near Obock. Djiboutian authorities are leading the response, mobilizing the Navy, army, police and health services, with support from IOM and UN partners. Arrivals, many of them women and young children, have been transported to the Markazi site in Obock, where they are receiving water, high-energy biscuits and hot meals. More are expected to flee as fighting intensifies.
+"Behind every number is a family who's lost everything," said Amy Pope, IOM Director General. "Many have been displaced multiple times. People are crossing the sea with nothing because they have no other choice left. Yemen is a country torn by poverty and conflict, and it cannot carry this crisis alone. I call on donors to scale up support now, for those arriving in Djibouti and for the communities in Obock receiving them."
+Fighting is escalating rapidly along the West Coast and South Taiz frontlines. Taiz remains the hardest hit, with 9,280 households, or nearly 56,000 people, displaced from districts including Jabal Habashy, Al Ma'afer, Maqbanah, Mawza and Al Wazi'iyah. Lahj follows with 3,225 households, or over 19,000 people, most from Al-Mudharibah district, with numbers rising in recent days. Al Hodeidah has recorded 1,374 households, or over 8,000 people, displaced, largely from Hays. Aden has also been affected with 424 households or over 2,500 displaced people being hosted there.
+Inside Yemen, families continue to flee multiple times, some for the second or third time in 12 years of conflict, with almost nothing left. Roads are increasingly inaccessible due to ongoing fighting, and communications in affected areas remain disrupted, making it harder to reach people and assess needs.
+IOM continues to call for safe, unimpeded humanitarian access, and for all parties to protect civilians, humanitarian workers, and the supplies, vehicles and facilities needed to deliver aid.
+The situation remains volatile and unpredictable. IOM will continue to monitor developments closely and report further updates as they become available.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:30.192092+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>IOM: Yemen Displacement Tops 76,000 as Fighting Intensifies</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-yemen-displacement-tops-76000-fighting-intensifies</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 12 September 2026 – The International Organization for Migration (IOM) is warning of a rapidly worsening displacement crisis in Yemen unfolding by the hour. At least 76,000 people have fled their homes since July, up from 46,000 just days earlier, according to IOM's Displacement Tracking Matrix (DTM) team and partners.
+Numbers have nearly doubled overnight. That's four times last week's total, as fighting intensifies. Entire families are on the move, often at night. They have nowhere safe to go.
+Fighting is escalating rapidly along the West Coast and South Taiz frontlines. Taiz is the hardest hit, with 8,300 households, or nearly 50,000 people, displaced from districts including Jabal Habashy, Al Ma'afer, Maqbanah, Mawza and Al Wazi'iyah. Lahj follows with 2,819 households, or almost 17,000 people, most from Al-Mudharibah district. Thousands more have fled Al Hodeidah, where 1,374 households, or over 8,100 people, have been displaced from coastal districts including Hays and Al Khawkha, where 191 households, or over 1,100 people, have fled.
+IOM Director General Amy Pope said families are being displaced for the second or third time in this conflict, with almost nothing left, and that spreading fighting is making it harder to reach people with lifesaving aid. She calls for safe, unimpeded access, and urged all parties to protect civilians and humanitarian workers, and to safeguard the supplies, vehicles and facilities IOM relies on to deliver help.
+Communications in affected areas remain disrupted. This is making it harder to reach people and assess needs. Roads are increasingly inaccessible due to ongoing fighting. This is further complicating an already dire situation.
+Many of these families have been displaced before, some multiple times, over 12 years of conflict. They are exhausted. Their resources are gone. Most fled with nothing but the clothes on their backs. They have left behind homes, livelihoods, and any sense of stability they had left.
+IOM teams are on the ground. They are distributing emergency supplies, including shelter materials, hygiene kits, and other essential items. But needs are far outpacing what we can deliver. The situation is deteriorating by the day. Displacement figures are expected to rise further in the coming days.
+We call on the international community to urgently scale up support for Yemen before this crisis deepens further.  The situation remains volatile and unpredictable. IOM will continue to monitor developments closely and report further updates as they become available.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:39.182438+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Displacement in Yemen Alarmingly Surges Past 46,000 Amid Escalating Fighting, IOM Chief</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/displacement-yemen-alarmingly-surges-past-46000-amid-escalating-fighting-iom-chief</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+11 September 2026
+Geneva, 11 September 2026 – At least 46,000 people have been displaced in Yemen since fighting escalated last week, the International Organization for Migration (IOM) said today. The number is alarmingly rising by the hour. IOM is calling on all parties to the conflict to guarantee safe humanitarian access and to protect civilians, aid workers and assets on the ground.
+“Families are being forced to flee for the second or third time in this conflict, with almost nothing left,” said Amy Pope, IOM Director General. “As fighting spreads, reaching people with lifesaving assistance is becoming harder. We urgently need safe, unimpeded access. All parties must protect civilians and humanitarian workers, and safeguard the supplies, vehicles and facilities we depend on to deliver help.”
+The figure spans the West Coast and Taiz governorates as of yesterday, and continues to climb. Overnight, large numbers of people were reportedly seen leaving Mokha city with their belongings. IOM's Displacement Tracking Matrix (DTM) team is working to establish updated figures to inform the humanitarian system and its lifesaving response, though communication with affected areas remains highly challenging due to widespread telecommunications disruptions.
+New arrivals are being reported Lahj and Aden Governorates, reports also indicate people are also moving North towards Ibb. Entire villages are reported to have emptied in Maqbanah, Jabal Habashi and Al Ma'afer as clashes moved closer to populated areas. The Mokha–Taiz road, a key supply route, has reportedly been cut, and host communities in the region are under growing strain.
+From the onset of the conflict, IOM has been responding to displaced populations through its Shelter, Land and Property, Camp Coordination and Camp Management (CCCM), and other field teams. Due to the deteriorating security environment, all operational movements have been temporarily suspended as of today.
+IOM calls on all parties to guarantee safe, sustained humanitarian access; to ensure the safety of aid workers, premises and assets across the country; and to restore the communications and transport routes needed to deliver assistance. Emergency stocks are already depleted from recent flood response, and the most urgent needs are shelter, food, water, household items, healthcare and protection support.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:47.659032+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>IOM Launches Crossroads Award to Recognize Those Transforming Lives, Nominations Now Open</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-launches-crossroads-award-recognize-those-transforming-lives-nominations-now-open</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+11 September 2026
+Geneva, 11 September – The International Organization for Migration (IOM) today announced the opening of nominations for the inaugural IOM Crossroads Award, a new initiative celebrating individuals, organizations, and initiatives that are transforming the lives of migrants, displaced persons, and the communities that welcome them.
+The Award recognizes those whose commitment and measurable impact advance safe, orderly and regular migration while upholding the rights, dignity, well-being and inclusion of people on the move.
+“Every day, we see migrants strengthening their communities, and people coming together to help those on the move find safety, rebuild their lives and contribute their skills,” said Amy Pope, IOM Director General. “As IOM marks its 75th anniversary, the Crossroads Award celebrates these contributions and the people who make them possible. By sharing their work, we hope to inspire others to turn compassion and good ideas into practical solutions that improve people’s lives.”
+The IOM Crossroads Award honours contributions from across society, including community organizations, civil society organizations, local leaders, volunteers, migrant-led initiatives, private sector partners, academic institutions, faith-based groups and host communities. Their work fosters protection, resilience, social cohesion and shared prosperity, demonstrating how collaboration and innovative solutions can create meaningful change.
+Rooted in IOM’s seventy-five-year legacy of supporting people on the move, the Award reflects the Organization’s enduring commitment to human dignity, solidarity and hope. Since its origins in 1951, when the Organization was established to assist people displaced by conflict in post-war Europe, IOM has evolved into the leading United Nations organization working on migration worldwide. The Award is founded on the belief that many of the most inspiring examples of leadership and impact happen closest to the communities IOM serves. The winner of the inaugural award will be announced at a special event marking IOM’s 75th Anniversary on 9 December 2026.
+For more information on the Award, including eligibility, selection criteria and how to nominate, visit https://www.iom.int/crossroads-award
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:52:54.650511+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Nepal Flood Death Toll Rises as Aid Needs Soar</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/nepal-flood-death-toll-rises-aid-needs-soar</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Kathmandu/Geneva 8 September 2026 – Humanitarian needs are growing rapidly in Nepal after devastating floods last month affected 84,000 people. The death toll has risen to 1,356 while nearly 4,900 remain missing, according to figures reported on 07 September by the National Disaster Risk Reduction and Management Authority (NDRRMA). Roads, bridges, health facilities, and schools have suffered extensive damage.
+As thousands of families struggle with displacement, loss and uncertainty, the International Organization for Migration (IOM) is appealing for USD 20.5 million to assist 43,000 people in support of the Government of Nepal-led response. Aligned with the inter-agency flash appeal launched by the UN and humanitarian partners, IOM's response focuses on strengthening displacement tracking and site coordination, while scaling up shelter, health, and protection assistance for displaced and affected communities.
+“For thousands of families, the immediate shock of the floods has been followed by immense uncertainty about their next steps," said Helene Fors, IOM Chief of Mission in Nepal. "Our priority is to ensure that humanitarian action is guided by reliable information and that critical assistance reaches those who need it most.”
+IOM teams are already on the ground supporting the response, including in hard-to-reach locations. IOM has conducted initial assessments at holding centres where displaced families are currently residing and has provided critical medicines to health authorities. However, sustained funding is required to expand assistance to affected communities.
+Priorities include emergency shelter support, particularly as winter approaches; access to health and psychosocial support services; and targeted protection support for people facing heightened risks, including women, children, older persons, and persons with disabilities.
+By expanding the use of its Displacement Tracking Matrix (DTM), IOM is also helping authorities to track displacement locations and population movements to identify urgent needs so assistance can be directed where it is needed most. As thousands of displaced people shelter in schools, monasteries, public buildings and host communities, IOM will help ensure they can access assistance, services and protection as co-chair of the Camp Coordination and Camp Management (CCCM) Cluster, led by the Department of Urban Development and Building Construction (DUDBC).
+IOM urges the international community to act now and help ensure that affected communities receive the assistance and protection they need.
+Download the IOM Flash Appeal – Nepal Flood Response.
+For further information please contact IOM Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:01.665387+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>18,500 Displaced in 72 Hours as Fighting Flares Across Yemen West Coast</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/18500-displaced-72-hours-fighting-flares-across-yemen-west-coast</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Aden/Geneva, 7 September 2026 — Renewed hostilities along Yemen's western coast and in parts of Taiz and Al-Hodeidah have forced thousands of people from their homes, with civilians reportedly among those killed and injured as clashes intensify.  
+Approximately 18,500 people have been displaced in the governorates of Taiz and Al-Hodeidah since hostilities escalated rapidly on September 3, according to the International Organization for Migration’s (IOM) Displacement Tracking Matrix, government and partners. The number is increasing by the hour as families continue to arrive in host communities and displacement sites.  
+“Families are arriving with nothing: no shelter, no food, no way to know if it's safe to go back,” said Abdusattor Esoev, IOM Yemen’s Chief of Mission. “Many of these are people who have already been displaced once, twice, even four times before. Every time fighting flares up, they lose whatever little they had managed to rebuild. We are particularly concerned by reports that some families may be unable to leave frontline areas safely because of continuing hostilities and insecurity along access routes.”  
+Reports indicate significant displacement from affected communities in Maqbanah, Al Ma’afer and Jabal Habashi, including Al-Hajab, Al-Rajehi, Hajjat Gabeh and Al Kadaha. Renewed fighting has also reportedly caused secondary displacement among families previously living in displacement sites in Hays.  
+Urban centres and host communities across South Taiz and the West Coast, including Al Mokha, Hays, Mawza, Al Ma’afer and Jabal Habashi, are experiencing significant pressure due to the continued influx of newly displaced families fleeing ongoing hostilities. With displacement figures continuing to rise, and local capacities overstretched, authorities have issued urgent appeals to humanitarian partners and UN agencies for additional support to address growing needs.  
+Challenges in road access due to ongoing clashes and disruption of telecommunications networks in the affected districts are slowing efforts to reach, register and verify newly displaced families, complicating an already difficult response. Emergency stocks, particularly food assistance, shelter and household items are severely depleted following recent flood and West Coast responses, leaving humanitarian partners with little to distribute to families arriving at reception sites.  
+Displaced families are urgently in need of cash assistance, emergency shelter, essential household items and food assistance. At reception sites and throughout host communities, access to safe drinking water and hygiene support remains problematic. In addition, affected populations urgently require emergency healthcare and referral pathways for the injured.  
+“At the same time, we recognize the presence of migrants using the Eastern Route who may also become trapped or stranded in these areas as a result of the deteriorating security situation and restrictions on movement. Their limited access to assistance, information, safe shelter, voluntary humanitarian return, and essential services may further increase their vulnerabilities and exposure to protection risks,” noted Esoev.   
+IOM is working alongside Yemen's Executive Units for Internally Displaced People and humanitarian partners to track, verify and consolidate displacement figures, identify people in urgent need, and mobilize resources for a rapid response.  Already, 663 households have been reached with vital household items across Taiz and Hodeidah governorates, while further supplies are on the way.  
+IOM calls on all parties to the conflict to protect civilians, allow safe passage for families trying to flee, and ensure unimpeded humanitarian access to those still trapped by the fighting.  
+The Organization is urging donors to urgently replenish emergency stocks and fund the response, as the scale of need continues to outpace available resources.  
+For further information please contact IOM Media Centre.  
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:08.572951+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>IOM Appeals for USD 110 Million to Protect 4.9 Million People Ahead of El Niño Impacts</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-appeals-usd-110-million-protect-49-million-people-ahead-el-nino-impacts</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 3 September 2026 – The International Organization for Migration (IOM) today appealed for USD 110 million to protect 4.9 million people from the potentially severe impacts of the developing 2026–2027 El Niño, including drought, flooding and extreme heat. The funding would allow IOM and its partners to act before humanitarian needs escalate: strengthening preparedness and early warning, supporting communities facing heightened displacement risks, pre-positioning essential assistance and helping authorities respond rapidly where people are forced to move.
+The 2026–2027 El Niño is unfolding in a world that is already warmer than during previous El Niño events. New forecasts released today by the World Meteorological Organization (WMO) indicate for the first time a near 100% probability that El Niño will persist through to February 2027. As a result, some areas may face severe drought, while others could experience heavier rainfall, flooding and extreme heat. For communities already struggling with conflict, displacement and food insecurity, these shocks can destroy harvests, disrupt livelihoods and water supplies, and force families to move.
+"Communities facing repeated climate shocks are often the first to recognize the warning signs. But without the right support, they cannot always act in time," said Deputy Director General of the International Organization for Migration (IOM), Ugochi Daniels. "Forecasts give us information we can act on. Flexible funding allows us to anticipate risks, strengthen preparedness and get support where it is needed most - helping people stay safe in their communities where possible, and helping those who need to move do so safely and with dignity."
+Past cycles show what is at stake. According to the World Food Programme, the 2015–2016 El Niño, one of the strongest on record, affected more than 60 million people worldwide through drought, flooding and other climate-related shocks. More recently, the 2023–2024 El Niño brought severe impacts across multiple regions, including Southern Africa, where nearly 68 million people were affected by drought. Shocks on this scale strain public services, erode livelihoods and can leave families with little choice but to move.
+Experiences from previous crises also show that acting on forecasts can reduce losses and humanitarian needs. IOM is part of inter-agency anticipatory action frameworks in 12 at-risk countries. In 2025, early support in five of them reached nearly 313,000 people in Haiti, Mozambique, Niger, Nigeria and the Philippines ahead of forecast shocks.
+With this funding, IOM will combine displacement analysis with weather and climate forecasts to identify where risks are likely to intensify and support earlier action. IOM will also strengthen people-centred early warning systems that alert authorities and communities to impending hazards and support timely evacuation. In pastoral areas, these systems can also provide advance warning of unusual or unseasonal movements that could increase pressure on communities and resources.
+Under the appeal, IOM will support governments to strengthen contingency planning through training and preparedness exercises and pre-position relief supplies near at-risk areas, enabling shelter, water, sanitation and hygiene, health and protection assistance to reach affected people quickly if access becomes constrained or conditions deteriorate.
+IOM will work with national and local authorities, United Nations agencies, non-governmental and community organizations, Red Cross and Red Crescent actors, and humanitarian coordination structures in priority countries across Asia and the Pacific; Eastern, Horn and Southern Africa; West and Central Africa; Latin America and the Caribbean; and selected contexts in the Middle East and North Africa.
+Flexible funding is important because the location and severity of El Niño impacts will continue to evolve over the coming months. Early contributions will allow IOM to direct resources rapidly to countries where forecasts and operational assessments indicate that action is most urgently needed.
+"Acting early saves lives and reduces suffering," said Daniels. "Forecasts cannot remove every uncertainty, but they give us time to prepare – and to reduce risks before needs escalate, lives are disrupted and more families are forced to move."
+The Global El Niño Appeal covers August 2026 to July 2027 and is available here.
+Support families affected by El Nino: Donate here.
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:23.891024+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>IOM and Amazon Partnership Aids Flood-Affected Communities in Nepal</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-and-amazon-partnership-aids-flood-affected-communities-nepal</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Kathmandu, 3 September 2026 – The International Organization for Migration (IOM) and Amazon are partnering to deliver critical support to communities affected by the devastating floods that struck central Nepal in August.
+The contribution will support government-led efforts to respond to widespread humanitarian needs following the disaster. As of 2 September, over 1,200 people are confirmed to have lost their lives and over 4,200 remain missing, while preliminary estimates show that more than 84,000 people have been affected. Damage to homes, roads, health facilities, and other critical infrastructure continues to hinder relief efforts.
+"The scale of this disaster has left many families grieving, displaced, and uncertain about what comes next," said Helene Fors, IOM Chief of Mission in Nepal. "Amazon's support comes at a critical moment, allowing us to provide assistance where it is most needed. We are grateful for Amazon's partnership and solidarity with the people of Nepal as communities begin the difficult process of recovery."
+Amazon’s flexible contribution will support IOM's response efforts, including activating the Displacement Tracking Matrix (DTM), delivering mental health and psychosocial support (MHPSS) services, and engaging communities on safe migration practices, the risks of human trafficking, and other protection concerns.
+Reliable data is essential for effective humanitarian action. Through DTM, IOM will support authorities and humanitarian partners to identify affected and displaced populations, monitor displacement trends, and assess priority needs. These insights will help inform response planning and enable humanitarian partners to better prioritize assistance for communities most in need. The floods have also taken a significant psychological toll on affected communities. IOM's MHPSS activities will help provide vital support to individuals and families coping with loss, vulnerability, and uncertainty in the aftermath of the floods.
+Amazon is also providing an in-kind donation of winterization kits, thermal blankets and solar lights with phone chargers to help address urgent shelter and relief needs among displaced households as winter approaches.
+This contribution builds on the longstanding partnership between IOM and Amazon in responding to humanitarian crises around the world. Together, the organizations have delivered life-saving shelter and relief assistance during emergencies in Türkiye, Syria, Mexico, Jamaica, and, most recently, Venezuela and Colombia, among others.
+Visit the IOM donation page for the Nepal floods to contribute.
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:32.278987+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>IOM Spokesperson Statement on Nepal-China Floods</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-spokesperson-statement-nepal-china-floods</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+27 August 2026
+Geneva, 27 August - The International Organization for Migration (IOM) is deeply saddened by the loss of life and widespread destruction caused by the recent floods along the Nepal-China border. We extend our heartfelt condolences to the families of those who have lost loved ones and stand in solidarity with all communities affected by this disaster.
+The floods have caused significant damage to homes, infrastructure and livelihoods, disrupting access to essential services and leaving many people in urgent need of assistance. As assessments continue, the full scale of humanitarian needs is still emerging.
+IOM stands ready to support relief and recovery efforts in China and Nepal, in line with identified needs and national priorities.
+In Nepal, IOM is already in close contact with authorities and humanitarian partners to contribute to a coordinated response. This builds on IOM’s long-standing partnership with the Government of Nepal, supporting previous disaster responses through shelter and non-food items, site management, health, data, early recovery and livelihoods.
+Send emergency aid to families in need: Donate here
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:39.252328+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>IOM Calls for Greater Investment in Land Restoration to Reduce Displacement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-calls-greater-investment-land-restoration-reduce-displacement</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Ulaanbaatar, 24 August 2026 – At the seventeenth session of the Conference of the Parties to the United Nations Convention to Combat Desertification (UNCCD COP17), the International Organization for Migration (IOM) is calling for significantly greater and earlier investment in land restoration, drought resilience and adaptation as a means of reducing displacement risks before they become humanitarian crises. The Organization emphasizes that land degradation, human mobility and security are deeply interconnected challenges that require integrated policy, financing and development responses. Through its engagement at COP17, IOM is urging governments, international financial institutions and partners to scale up action and financing that protect livelihoods, strengthen resilience and preserve people’s ability to stay, move safely or return with dignity.
+Today, IOM is co-leading the Thematic Day on Finance, including a high-level Ministerial Dialogue on Land, Migration and Security, bringing together governments and partners to identify practical pathways for translating commitments into investments that strengthen resilience and support communities facing drought, desertification and land degradation.
+“We are still much better at financing the consequences of displacement than investing early enough to reduce its risk,” said Ugochi Daniels, IOM Deputy Director General. “When land fails, people lose the ability to choose: to stay, to move safely, or to return with dignity. With USD 878 billion lost every year to degraded land, the costs to economies and communities are already enormous. Investing in restoration is also an investment in resilience, livelihoods and people’s ability to keep these choices open.”
+Held under the theme “Restoring Land. Restoring Hope,” COP17 comes as up to 40 per cent of the world’s land is degraded, affecting half of humanity. As land deteriorates, communities can lose access to the food, water, productive land and livelihoods that enable people to remain safely where they are.
+Today, close to two-fifths of humanity, some 3.2 billion people, live in areas affected by land degradation. Weather-related disasters alone have driven some 200 million internal displacements over the past decade, underscoring the need for stronger investments in resilience and adaptation.
+The International Year of Rangelands and Pastoralists also serves as a reminder that women, young people, migrants and displaced communities are not passive victims of land degradation. They are leaders, innovators and partners in building resilience and must be part of shaping the solutions.
+IOM is also calling for stronger connections between evidence, policy, solutions and investment. Understanding where drought, desertification and land degradation are most likely to undermine livelihoods and contribute to human mobility can help governments and partners identify where investment is needed most, develop locally led solutions and direct financing towards communities before risks become crises.
+These priorities are reflected across IOM’s programming showcased at COP17. IOM is supporting the Peace Forest Initiative for the Horn of Africa, an estimated USD 30 million programme to restore degraded land and strengthen the resilience of communities facing climate pressures, while integrating human mobility considerations in fragile border areas.
+Beyond COP17, IOM and UNCCD are advancing a new Joint Roadmap for Action 2026–2030 as part of their renewed partnership, setting out how the two organizations will work together on land degradation, drought and human mobility, and translate global commitments into practical action at country and community levels.
+Young people are also contributing to this effort, with IOM sponsoring youth delegates from the UNCCD Youth Caucus to ensure youth voices are part of discussions on land, climate and human mobility.
+“Coming from the Sahel, where communities live with the realities of drought, desertification and land degradation, being at COP17 means having our voices heard on the global stage,” said one of the youth delegates. “We want to move from policy to action, from action to programmes, and from programmes to the communities that need them.”
+Speaking at today’s Thematic Day on Finance, IOM reaffirmed its commitment to work with Member States, international financial institutions, the private sector and civil society to mobilize new sources of investment and turn commitments on land restoration into practical and scalable solutions.
+The message from COP17 is clear: investing earlier in healthy land, resilience and adaptation is not only an environmental imperative. It is an investment in people, helping reduce displacement risks, strengthen livelihoods and build more resilient communities. IOM stands ready to work with partners to turn commitments into practical, scalable solutions that deliver results where they are needed most.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:47.489147+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Rwanda Highlights Potential for Migration to Drive Jobs, Skills and Regional Growth: IOM Chief</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/rwanda-highlights-potential-migration-drive-jobs-skills-and-regional-growth-iom-chief</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+21 August 2026
+Kigali, 21 August 2026 – Rwanda is demonstrating how well-managed migration can create jobs, build skills and strengthen regional cooperation. Over the past two decades, Rwanda has emerged as a leading voice on migration in Africa, integrating migration into national development planning and working to promote safe and regular migration.
+“Rwanda is showing how investment in skills, labor mobility and protection can turn migration into an opportunity for people and economies,” said International Organization for Migration (IOM) Director General Amy Pope at the conclusion of her official visit to Rwanda today. During the visit, Director General Pope met with Hon. Dr. Justin Nsengiyumva, Prime Minister of the Republic of Rwanda, as well as senior Government officials, development partners, United Nations representatives, and migrants supported by IOM. “I was grateful for the opportunity to engage with Hon. Prime Minister Dr. Justin Nsengiyumva and other leaders to discuss how labor mobility, skills development, diaspora engagement and protection can help people while supporting national and regional priorities,” said Pope. "IOM remains committed to supporting efforts to strengthen protection and expand pathways for safe, orderly and regular migration.”
+The visit also provided an opportunity to discuss emergency preparedness, skills development, anti-human trafficking efforts and support for returning migrants rebuilding their lives.
+Pope also met with development partners, international financial institutions, private sector representatives and members of the United Nations Country Team to explore stronger collaboration on skills development, labour mobility and economic growth.
+Throughout the visit, DG Pope emphasized the importance of international cooperation to tackle migration challenges and maximise the benefits of migration, including by tapping into the vast development potential of diaspora engagement.
+“No country can address migration challenges alone,” Pope said. “Continued cooperation between governments, international partners and the private sector is essential to expanding opportunities and ensuring migration works for people and communities.”
+IOM reiterated its commitment to working with the Government of Rwanda and partners to strengthen protection, expand safe mobility pathways and support efforts that benefit migrants and communities and economies across the region.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:53:56.119382+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Tanzania at Heart of East Africa Migration Response, IOM Chief Says</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/tanzania-heart-east-africa-migration-response-iom-chief-says</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Dar es Salaam, Tanzania, 19 August 2026 – The United Republic of Tanzania and the International Organization for Migration (IOM) are strengthening cooperation on safe and regular migration, labour mobility, migrant protection and climate-related mobility, as countries across East and Southern Africa work together to respond to growing migration pressures and opportunities.
+Migration remains a defining feature of the region, which hosts more than 12.7 million international migrants, over 16 million internally displaced people and approximately 5.4 million refugees.
+“Tanzania is at the heart of some of the most important migration conversations taking place in Africa today,” said IOM Director General Amy Pope. “From labour mobility and skills development to refugee protection and climate-related displacement, regional cooperation can help turn migration into an opportunity for people, communities and economies.”
+As a country of origin, transit, destination and refuge, Tanzania serves as a key hub for migration dialogue and coordination across East and Southern Africa. The country currently chairs the Regional Ministerial Forum on Migration and hosts IOM's African Capacity Building Centre (ACBC), which supports migration governance and professional training across the continent.
+During her visit to the United Republic of Tanzania this week, Pope met President Samia Suluhu Hassan, government officials, United Nations partners and migration stakeholders to discuss migration governance, labour mobility, border management, climate mobility and regional cooperation.
+Discussions focused on advancing Tanzania's National Migration Policy, strengthening migration coordination, border and data systems, and supporting safe and regular mobility across the region. DG Pope also joined the launch of the country’s National Coordination Mechanism on Migration and took part in the handover of the Chairpersonship of the Regional Ministerial Forum on Migration for East and Horn of Africa.
+The need for stronger regional cooperation is also underscored by growing climate and displacement pressures. Climate-related movements across the region increased by 16% in 2024, highlighting the importance of policies that strengthen emergency preparedness and regional cooperation. 
+Pope also highlighted Tanzania's contribution to regional capacity-building through institutions such as the African Capacity Building Centre in Moshi and the Tanzania Regional Immigration Training Academy.
+The Migration and Urbanization Monograph, launched in 2026 and drawing on data from the 2022 Population and Housing Census, indicates that Tanzania hosts more than 280,000 international migrants. This highlights the importance of evidence-based migration governance and informed policymaking to maximize the benefits of migration while addressing its challenges. 
+IOM and the Government of Tanzania have worked together for decades to advance migration governance, labour mobility, migrant protection, migration health and climate resilience. The visit reinforced a shared commitment to promoting safe, orderly and regular migration while supporting development and stability across the region. 
+For more information please visit IOM's Media Centre. 
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:05.348412+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Sudan: 200,000 Newly Displaced as Fighting and Floods Intensify, Closure of Red Sea and Strait of Hormuz Threatens Critical Aid</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/sudan-200000-newly-displaced-fighting-and-floods-intensify-closure-red-sea-and-strait-hormuz-threatens-critical-aid</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Khartoum, 19 August 2026 – Sudan is facing mounting displacement and humanitarian pressures as escalating conflict and destructive seasonal flooding compound an already grave humanitarian situation, even as significant numbers of people return to Khartoum. Humanitarian access is further disrupted by delays in global supply chains, particularly through the Red Sea and Strait of Hormuz, adding pressure to an already fragile response.
+The country has 8.6 million people internally displaced and significant cross‑border movements into neighbouring countries. In other parts of the country, escalating conflict, repeated attacks on infrastructure, and destructive seasonal flooding are compounding humanitarian needs and stretching families beyond their limits.
+“The warning signs are impossible to ignore. Across Sudan, families are fleeing violence, losing access to water, electricity, and health care, and now facing the added burden of destructive floods. Without urgent action to protect civilians and restore essential services, the suffering will deepen,” said IOM Director General, Amy Pope, as the Organization continues its humanitarian response.
+In North Kordofan, intensified fighting and drone strikes on El Obeid’s main electrical transformer triggered prolonged power outages, disrupting water pumping, health facilities, and telecommunications. Displacement has surged by 25 per cent in Sheikan locality over the past eight months, with more than 200,000 people newly displaced across the wider Kordofan region since late 2025. In Blue Nile, clashes in and near Geissan displaced 7,800 people, some crossing into Ethiopia. Meanwhile, in West Darfur nearly 18,000 people were displaced in the first half of August.
+Heavy rainfall in Tawila, North Darfur, destroyed or damaged nearly 1,350 homes last week, displacing over 1,000 families, while additional flooding in Kabkabiya and Shangil Tobaya forced dozens of families into temporary shelters.
+Despite these challenges, IOM is scaling up its response. Over the last 72 hours, the Organization delivered 1,750 metric tonnes of humanitarian supplies, including 17,750 hygiene kits and 850 tents, already directly benefiting 110,750 people in areas where needs are most acute. This will rise to over 400,000 over the coming days.
+“Sudan is one of the world’s largest displacement crises. The combined impact of conflict, infrastructure damage, and flooding is stretching thousands of families beyond their limits,” added Pope. “IOM is committed to delivering life-saving aid, but urgent support is needed to sustain shelter and pipeline operations before conditions worsen further.”
+With funding for shelter interventions sharply declining, IOM calls for enhanced support to ensure continued delivery of assistance to millions of people affected across Sudan. 
+For more information please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:13.691126+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Migration Routes Grow Dangerous Even as Irregular Arrivals Fall in 2026, New IOM Data Show</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/migration-routes-grow-dangerous-even-irregular-arrivals-fall-2026-new-iom-data-show</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 12 August 2026 – Migrant deaths more than doubled along the Central Mediterranean Route and tripled along the Eastern Mediterranean Route in the first four months of 2026 compared with the same period in 2025, even as the number of people arriving in Europe fell sharply, according to new data released today by the International Organization for Migration (IOM).
+New IOM route-based data show that severe weather, conflict, economic pressure and changing migration policies reshaped migration journeys across multiple regions during the first four months of 2026. Along the Central Mediterranean, 821 people died or went missing, an increase of 111 per cent, while arrivals fell by 46 per cent to 8,577. More than half of those deaths, 430, were recorded in January alone, when Cyclone Harry struck the region. Along the Eastern Mediterranean, 244 people died, a rise of 259 per cent, with many fatalities linked to sea crossings that ended in disasters near Crete.
+"Fewer arrivals do not mean safer journeys," said IOM Deputy Director General Ugochi Daniels. "Behind every one of these numbers is a family waiting for news that never comes. As journeys grow longer and more dangerous, saving lives at sea and on land remains a shared responsibility, and one that no country can meet alone."
+IOM data also show that along the Western African Atlantic Route, arrivals to Spain fell by 78 per cent to 2,276, the steepest decline of any route to Europe. Departure points have continued to shift further south along the West African coast, lengthening the sea crossing and raising the risks people face.
+Not all routes saw declines. Arrivals to Spain along the Western Mediterranean Route rose by 66 per cent to 5,647, driven largely by a threefold increase in land crossings to Ceuta and Melilla. Arrivals in Yemen along the Horn of Africa Eastern Route rose by 9 per cent to 70,200, in line with seasonal patterns. In Central America, northbound movement through Panama's Darién region has almost stopped, with 135 transits recorded.
+Hostilities in the Middle East also impacted mobility patterns across the region and beyond during the reporting period. Following the escalation that began in late February, large-scale displacement was recorded in Lebanon and cross-border returns to the Syrian Arab Republic rose through March and April, while pressure grew on labour migration and remittance flows across South Asia, the Middle East and Africa.
+"Attention tends to settle on a handful of routes, but nearly half of the world's 304 million international migrants live within their own region, moving for work, family, education and safety," said Daniels. "Good data is not a substitute for solutions, but there are no solutions without it. When everyone is working from the same clear picture, better decisions follow."
+The Global Overview of Migration Routes (January to April 2026) brings together data from IOM's Displacement Tracking Matrix (DTM), IOM’s Missing Migrants Project, Regional Data Hubs and government partners to track migration trends across major routes worldwide.
+Download the Report here.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:20.906543+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>IOM Spokesperson Statement on Colombia Earthquake</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-spokesperson-statement-colombia-earthquake</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+11 August 2026
+Geneva, 11 August 2026 – "The International Organization for Migration (IOM) is deeply saddened by the 7.4 magnitude earthquake that struck western and central Colombia on the morning of 10 August. The event has already caused hundreds of deaths and injuries, with hundreds more reported missing. Homes have been destroyed and essential infrastructure services such as water, energy, health, education, and telecommunications have been seriously disrupted.
+Our thoughts are with everyone who has been affected and we stand in solidarity with the people of Colombia and with the rescue teams and first responders working tirelessly to save lives.
+IOM teams are ready to deploy and to assess the most urgent needs in close coordination with the National Government and the National Unit for Disaster Risk Management, local authorities, and humanitarian organizations present in the affected areas. Building on 70 years of partnership with Colombia, IOM stands ready to support the Government of Colombia with emergency shelter assistance and essential relief items for people displaced by the disaster, while working alongside United Nations humanitarian partners to address urgent needs, including water, sanitation and hygiene services and psychosocial support. 
+In an emergency of this scale, every minute counts. IOM calls on the international community to support the response and stand with the people of Colombia."
+Visit the IOM donation page Emergency Colombia Earthquake to contribute.
+For more information, please visit IOM's Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:27.885880+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>IOM Chief’s Türkiye Visit Highlights Country’s Role in Shaping Future of Migration Governance</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-chiefs-turkiye-visit-highlights-countrys-role-shaping-future-migration-governance</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+07 August 2026
+Ankara, 7 August 2026 – International Organization for Migration (IOM) Director General (DG) Amy Pope visited Türkiye for high-level discussions with government counterparts and partners on migration governance, regional stability and development, highlighting the country's growing role in shaping responses to regional mobility challenges. Positioned at the crossroads of Europe, Asia and the Middle East, Türkiye plays a pivotal role in regional migration governance and cooperation, drawing on extensive experience in displacement, labour mobility, social cohesion, climate-related migration and voluntary returns. As migration patterns continue to evolve, discussions focused on strengthening cooperation to support resilience, economic opportunity and regional stability.
+The visit comes as IOM marks 35 years of operations in Türkiye. Since establishing its presence in 1991, IOM has worked alongside national and local institutions, communities and international partners to support migration management, humanitarian response, disaster preparedness, labour mobility, social cohesion and evidence-based policymaking. Today, that cooperation increasingly focuses on long-term solutions that support regional connectivity, stability and shared prosperity.
+"Türkiye demonstrates that when migration is supported by effective policies and coordinated action, it can move beyond a crisis-response to become a catalyst for economic growth and resilience," said DG Amy Pope.
+Pope highlighted Türkiye's growing contribution to regional and global discussions on migration policy and practice. Discussions also explored how the country's experience can help inform responses to key mobility challenges, including displacement preparedness, labour mobility and safe and dignified voluntary returns.
+There was focus on Syria's recovery. Particular focus was given to how investments in job opportunities and skills development can help communities, support long-term recovery and contribute to regional stability as people return.
+"As mobility dynamics continue to evolve, countries have an opportunity to transform migration from a challenge to be managed into an opportunity to strengthen communities, address labour market needs and build a more prosperous future,” adds DG Pope. “That requires long-term vision, strong partnerships and investments that benefit both people on the move and the communities that host them."
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:37.570501+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>IOM Assists 17.8 Million People Worldwide Despite Growing Humanitarian Funding Gap</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-assists-178-million-people-worldwide-despite-growing-humanitarian-funding-gap</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+05 August 2026
+Geneva, 05 August 2026 – More than 300 million people needed humanitarian assistance in 2025 as conflicts, disasters and displacement pushed global needs to record levels, while funding for aid fell sharply.
+Despite mounting pressure across the humanitarian sector, the International Organization for Migration (IOM) reached 17.8 million people in 170 countries and territories through USD 1.7 billion in humanitarian and recovery programmes, according to figures released today.
+From the Sudan and Gaza to Haiti, Myanmar and the Sahel, crises intensified throughout the year, forcing aid agencies to make increasingly difficult decisions about where limited resources could be deployed.
+"2025 was a year of extraordinary pressure for the humanitarian system," said IOM Deputy Director General for Operations Ugochi Daniels. "Conflicts, disasters, disease outbreaks and displacement drove needs to unprecedented levels, even as resources contracted dramatically. Despite these challenges, IOM remained present where people needed us most."
+According to IOM's 2025 Operating in Crisis Report, the Organization provided shelter assistance to 7.3 million people, supported 5.1 million people with water, sanitation and hygiene services, delivered 4.2 million primary health consultations, and provided protection assistance to 1.5 million people. It also helped more than 760,000 people move to safety through evacuations, relocations and other forms of movement assistance.
+Beyond direct assistance, IOM continued to play a key role in helping the wider humanitarian community respond to crises. Its Displacement Tracking Matrix, the world's largest source of operational displacement data, informed 21 of 23 Humanitarian Needs and Response Plans globally in 2025, helping governments and aid organizations target assistance where it was needed most.
+The report also highlights IOM's growing work along major migration routes, tracking risks and needs across borders to help governments and partners better understand how people move during crises and where support is most urgently required.
+As humanitarian needs continue to outpace available funding, the report underscores the importance of making humanitarian action more efficient, coordinated and evidence-based to ensure limited resources reach those most in need.
+The 2025 Operating in Crisis Report is available here.
+For more information, visit the IOM Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:46.260091+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>IOM Hands Over Vaccine Transport Trucks to Strengthen Immunization Services Across Southern Iran</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-hands-over-vaccine-transport-trucks-strengthen-immunization-services-across-southern-iran</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Tehran, 29 July 2026 – The International Organization for Migration (IOM) handed over two specialized vaccine transport trucks to health authorities in the Islamic Republic of Iran, helping strengthen the safe and timely delivery of vaccines to migrants and host communities across southern and southwestern parts of the country.
+The support was provided in response to a request from the Center for Management of Communicable Diseases of the Ministry of Health and Medical Education and was channeled through IOM Iran’s principal government counterpart, the Center for Aliens and Foreign Immigrants Affairs (CAFIA) of the Ministry of Interior.
+The handover comes at a time when heightened tensions across the Middle East continue to affect civilian populations, infrastructure and essential services. The United Nations has repeatedly called for restraint, protection of civilian infrastructure, and renewed diplomatic efforts to prevent further humanitarian consequences across the region.
+Each refrigerated vehicle has a carrying capacity of six tonnes and is specifically designed for the transportation and distribution of vaccines. Equipped with a dual-mode operating system and specialized cold-chain equipment, the trucks will help preserve vaccine integrity and strengthen delivery to health facilities across the country.
+“Access to health services, including routine immunization, remains essential for the health and well-being of communities,” said Salvador Gutierrez, IOM Iran Chief of Mission. “By strengthening vaccine distribution networks, this support will help ensure that vital vaccines reach people safely and efficiently, including those living in remote and underserved areas.”
+The two vaccine trucks designed for bulk vaccine transportation, procured by IOM for the Ministry of Health will be deployed to regional distribution hubs in Khuzestan and Fars provinces, strengthening Iran’s national vaccine cold chain system. Through these centers, vaccines and biological products will be distributed to health facilities serving the population covered by the Universities of Medical Sciences in Shiraz, Fasa, Jahrom, Gerash, Larestan, Ahvaz, Shushtar, Abadan, Behbahan, and Dezful.
+The initiative is intended to benefit both migrants and host communities in urban and rural areas, particularly vulnerable groups with limited access to health services. By reinforcing vaccine distribution capacity, the intervention will contribute to improved access to immunization services and enhanced vaccination coverage in communities served by the two hubs.
+Iran hosts one of the largest migrant populations in the region, including millions of Afghans who rely on public services alongside host communities. Maintaining resilient health systems and reliable vaccine distribution remains especially important as regional instability continues to place pressure on infrastructure, mobility and essential services.
+International concern over further escalation in the Middle East remains high. The United Nations Secretary-General has renewed calls for restraint, protection of civilian infrastructure, restoration of navigational freedoms, and renewed diplomatic engagement.
+The new vehicles will help strengthen those distribution networks, supporting continued access to essential immunization services for both migrants and host communities while reinforcing the capacity of local health systems to reach remote and hard-to-reach populations. The intervention was made possible through funding from the Ministry of Foreign Affairs and International Cooperation of Italy.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:54:54.506035+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>"Trapped Behind the Scam": IOM Warns Trafficking Victims Are Being Forced into Scam Networks</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/trapped-behind-scam-iom-warns-trafficking-victims-are-being-forced-scam-networks</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva, 28 July 2026 – Hundreds of thousands of people worldwide have been trafficked by criminal networks and forced to participate in online scams in a multibillion-dollar criminal industry, the International Organization for Migration (IOM) warns today, in advance of 30 July which marks World Day Against Trafficking in Persons under the theme "Trapped Behind the Scam."
+Trafficked victims are often lured by fake job ads promising legitimate work abroad. Once they arrive, many are locked inside compounds, stripped of their documents, subjected to constant surveillance, and forced through violence, threats and debt bondage to carry out online scam operations targeting people worldwide. Survivors report enduring torture, sexual abuse, starvation and solitary confinement.
+"People trapped in scam compounds are victims of trafficking, forced to commit crimes through violence, threats and coercion. They deserve protection, not punishment," said IOM Director General Amy Pope. "We must work together to support survivors, stop traffickers and close the gaps these criminal networks exploit. No country can tackle this alone."
+The scale of the crime is staggering. New United Nations Office on Drugs and Crime (UNODC) data estimates combined annual losses from scam offences across East Asia, South-East Asia, Australia, and New Zealand are between USD 88.3 billion and USD 114.1 billion for 2025 alone, much of it tied to organized crime, and scam compounds across the region are believed to hold hundreds of thousands of trafficked workers.
+As trafficking in persons for forced criminality continues to expand across Asia and increasingly beyond the region, IOM has launched its new Regional Strategy Response to Trafficking in Persons for Forced Criminality in Asia and the Pacific (2026–2030). The strategy outlines IOM's vision for addressing one of the fastest-growing forms of human trafficking, with a strong focus on victim protection, prevention, cross-border cooperation and stronger partnerships to disrupt trafficking networks.
+Between 2022 and 2025, IOM assisted more than 3,500 victims of trafficking for forced criminality across South-East Asia, from 39 countries, with the largest numbers originating from Indonesia, India, Sri Lanka, Ethiopia, Kenya, and Bangladesh.
+The message at the heart of this year's campaign is clear: people forced to commit crimes inside scam centres are victims of trafficking, not criminals, and should be protected, not punished.
+Rescue is only the first step. Survivors often face severe trauma, stigma, debt, missing identity documents and the fear of prosecution, requiring sustained support to return home safely and rebuild their lives. IOM's response includes identifying victims, referring them to protection services, providing direct assistance, coordinating with consular authorities, supporting safe return and reintegration, and working with governments and law enforcement partners to strengthen victim identification, cross-border cooperation and accountability for traffickers.
+To strengthen its response, IOM calls for continued support to assist victims of trafficking through protection, safe return and reintegration, while scaling up efforts to raise awareness of traffickers’ tactics so that people can recognize risks and know where to seek help.
+To support victims of trafficking, donate here.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:01.009332+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>3.9 Million People Displaced in Ukraine as Families Struggle to Cope, IOM Report Finds</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/39-million-people-displaced-ukraine-families-struggle-cope-iom-report-finds</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Kyiv/Geneva, 27 July 2026 – An estimated 3.9 million people remained internally displaced in Ukraine as of June 2026, according to a new report by the International Organization for Migration (IOM). While the number of internally displaced people has stayed at around 12 per cent of the population since 2023, the report shows that the longer displacement persists, the more families are struggling to meet their basic needs.
+Nearly seven in ten internally displaced people have now been away from home for more than two years, underscoring the increasingly protracted nature of displacement in Ukraine. New displacement is also still happening: an estimated 132,000 people were forced to leave their homes between January and June this year alone.
+“Stable displacement figures should not be mistaken for stable living conditions,” said Dejan Keserovic, Deputy Chief of Mission at IOM Ukraine. “Many displaced families are exhausting their savings, reducing essential expenses, including health care, and moving into less adequate housing as they try to meet their basic needs. Sustained support remains essential to help people regain stability and make informed, voluntary choices about their future.”
+The report found that 87 per cent of displaced households have had to take at least one difficult step to cope. The most common include using up savings (75%), cutting back on utilities (59%) and reducing health spending (53%). One in five households also reported moving to lower-quality housing, while 17 per cent have fallen behind on rent.
+The pressure has been building steadily — last winter's harsh weather and long power and heating outages hit already-vulnerable families particularly hard.
+Safety remains the biggest factor in people's decisions about the future: 82 per cent of internally displaced people say they only want to return home once the fighting stops. At the same time, more people are considering settling permanently where they now live — interest in local integration increased from 51 per cent in March to 58 per cent in June 2026, highlighting the need to support displaced families wherever they are, while still keeping an eye on the risks of people returning too soon or unsafely.
+Around 2.15 million individuals – 56 per cent of all those displaced in Ukraine – originally came from areas that were fully or partly occupied at the time of the survey. This group has faced longer displacement, greater hardship, and fewer options for going home.
+The findings show why emergency aid alone isn't enough. People need longer-term support with housing, jobs, health care, protection, and other essential services — so they can make informed, voluntary choices, whether that means settling where they are, moving elsewhere, or returning home safely once conditions allow.
+The report is based on IOM's latest survey of the Ukrainian population, carried out between 23 April and 30 June 2026, with support from the Government of Canada, the European Union, Sweden, and the Ukraine Humanitarian Fund.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:09.766824+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Afghanistan Floods Again: Communities Never Get Time to Recover</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/afghanistan-floods-again-communities-never-get-time-recover</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Kabul/Geneva, 23 July 2026 - Responding to the flash floods that began on 20 July and affected nine provinces across Afghanistan, with Nuristan the hardest-hit province, the International Organization for Migration (IOM) Spokesperson said:
+"What we're seeing in Nuristan is devastating. Families have lost everything in a matter of hours — homes, shops, roads, swept away. Rescue teams are operating in one of the most remote and hard-to-reach parts of the country, digging through rubble by hand, with the constant risk of more flooding.
+"IOM teams are on the ground assessing the needs of affected communities, and our trucks are already on the way with life-saving relief supplies. Across Afghanistan, communities barely have time to recover before the next disaster hits. This is the reality of climate vulnerability layered on top of years of conflict and fragile infrastructure. People simply do not have the resources or resilience left to absorb repeated shocks.
+"Families who have lost their homes need shelter, clean water, and support to rebuild — not only in the immediate aftermath of a disaster, but in the months that follow. The International community must step up efforts and must not look away from Afghanistan. Humanitarian needs are urgent, and they are growing."
+Background
+Flash floods that began on 20 July 2026 affected nine provinces across Afghanistan, with Nuristan bearing the brunt of the devastation. According to Afghanistan's National Disaster Management Authority (ANDMA), at least 23 people have died, around 80 have been injured, and more than 100 remain missing as of 21 July.
+The provincial capital, Parun, was among the hardest-hit areas, where homes and other infrastructure were severely damaged. Search and rescue operations are continuing under difficult conditions amid the ongoing risk of further flash flooding.
+This latest emergency is not an isolated event. Afghanistan has faced repeated flooding throughout 2026. Between March and May, floods and other climate-related hazards affected more than 11,000 families (over 82,000 people). Humanitarian assistance reached 75 per cent of those affected across the country, with the Eastern Region among the hardest hit areas. The disasters damaged more than 11,000 shelters, while also affecting critical water infrastructure and increasing risks related to access to safe drinking water and sanitation.
+Earlier nationwide floods in March and April killed 99 people and injured 154. More than 5,000 homes were destroyed, 355 kilometres of roads were washed away, and over 14,000 acres of farmland were inundated. Climate variability, including the influence of El Niño, is contributing to increased risks of extreme weather events across Afghanistan. These hazards are compounded by decades of conflict, environmental degradation, and limited coping capacity, leaving communities increasingly exposed to recurrent disasters.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:18.149271+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>IOM Chief visits Guyana, highlighting migration as force for growth</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-chief-visits-guyana-highlighting-migration-force-growth</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Georgetown, Guyana, 23 July 2026 — Guyana is one of the fastest-growing economies in the world, and its expanding industries are creating rising demand for workers. This week, Amy Pope, Director General of the International Organization for Migration (IOM), visited Guyana to discuss opportunities to strengthen IOM’s support to the Member State in managing migration to help power that growth.
+Guyana's economy is expanding rapidly — its real GDP grew by 19.3 per cent in 2025, according to the Bank of Guyana — driven by growth in energy, construction, healthcare and other sectors, creating strong demand for workers that outpaces the domestic labour supply. At the same time, significant numbers of Guyanese have migrated, representing a potential pool of skills, resources and connections the country could draw on. Together with workers from CARICOM and the wider region, this presents an opportunity for Guyana to address labour shortages, continuing to upskill the local labour force, while building a migration system that safeguards the rights and wellbeing of migrants and Guyanese host communities.
+"Migration has always been part of Guyana's development story," said Director General Amy Pope. "When it's managed well, it creates opportunities for everyone — local communities, returning Guyanese, and migrants from the region and beyond. Guyana is uniquely positioned to turn migration into a real force for development, and IOM is committed to helping the government build practical solutions that get real results for a broad cross-section of Guyanese society."
+During her trip, DG Pope met with five Ministers of Government, reflecting how migration touches so many parts of society. She also met with migrants and with IOM staff working across Guyana and the Caribbean. These engagements were intended to ensure that migration policies and programmes remain grounded in the needs of the people they serve, connecting workers with employment opportunities while protecting migrants' rights and supporting community wellbeing.
+DG Pope also met with the Caribbean Community (CARICOM) Secretariat, which is headquartered in Guyana. As Coordinator of the UN Network on Migration, IOM has been providing technical support to CARICOM, working with countries across the Caribbean to help develop a regional migration governance framework. This framework would support national migration policies that respond to both shared and country-specific migration and labour challenges, including how nations adapt to climate change and shrinking productive populations while sustaining economic growth.
+IOM has worked in Guyana since 2009, helping the government strengthen migration management in line with its development goals to ensure broad opportunity for Guyanese and the government’s commitment to safe, orderly and regular migration. In this work, IOM draws on its global expertise in areas such as border management, migration data, and protection and assistance for vulnerable migrants and host communities, helping translate national priorities into practical action.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:24.909484+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Africa CDC and IOM Sign New Partnership to Strengthen Africa’s Health Security</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/africa-cdc-and-iom-sign-new-partnership-strengthen-africas-health-security</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Addis Ababa / Geneva, 22 July 2026 – The Africa Centres for Disease Control and Prevention (Africa CDC) and the International Organization for Migration (IOM) have signed a new Cooperative Agreement to strengthen Africa’s capacity to prevent, detect and respond to public health threats across the continent.
+The agreement sets out how the two organizations will work together from 2026 to 2028, combining Africa CDC’s leadership in public health and IOM’s global operational expertise in supporting the health of migrants, displaced people and mobile populations. Together, they will support African Union Member States to strengthen preparedness, improve disease surveillance, expand equitable access to health services and build stronger public health systems.
+The partnership comes at a time when disease outbreaks, climate-related health risks and population movements increasingly shape Africa’s public health landscape. Stronger cross-border collaboration will help countries detect threats earlier, coordinate responses more effectively and protect communities wherever they live or move.
+“Health threats move across borders. Africa’s response must move together,” said H.E. Dr Jean Kaseya, Director General of Africa CDC. “This partnership strengthens our collective ability to anticipate risks, coordinate action and support Member States with stronger surveillance, preparedness and emergency response. It advances Africa’s Health Security and Sovereignty Agenda through practical cooperation that protects lives and strengthens public health systems across the continent.”
+The Cooperative Agreement builds on collaboration between Africa CDC and IOM that began during the COVID-19 pandemic and expands cooperation across several strategic priorities.
+Africa CDC and IOM will work together to strengthen preparedness and emergency response while ensuring that migrants, displaced and mobile populations are not left behind. The partnership will improve disease surveillance, strengthen health measures at Points of Entries (PoEs) and support early warning systems, allowing countries to detect health threats earlier, share information more quickly and coordinate across borders.
+The agreement also expands cooperation to improve access to primary health care, immunization and disease prevention services for migrants, displaced people and mobile populations. Joint programmes will strengthen the public health workforce through training, deployment and rapid-response support. They will also help countries better address the health impacts of mobility, displacement and climate-related health risks in national preparedness plans, health policies and disease control efforts. The partnership will also support sustainable financing for preventing and responding to future health emergencies.
+Implementation will be guided through joint technical working groups that bring together experts from both organizations on disease surveillance, workforce development, access to essential health services, climate and One Health, governance, policy and resource mobilization and other priority areas.
+“Effective public health systems protect people wherever they live, work or move,” said Frantz Celestin, Regional Director for East, Horn and Southern Africa at IOM. “This partnership strengthens countries’ capacity to prepare for health emergencies, improve cross-border collaboration and expand access to essential health services for migrants, displaced populations and border communities across Africa.”
+The Cooperative Agreement provides a platform for long-term cooperation, joint programmes and coordinated support to African Union Member States. It reinforces the shared commitment of Africa CDC and IOM to stronger institutions, more resilient health systems and a healthier, safer Africa.
+About Africa CDC
+The Africa Centres for Disease Control and Prevention is the autonomous public health agency of the African Union. Africa CDC supports African Union Member States in preventing, detecting and responding rapidly and effectively to disease threats and public health emergencies while strengthening public health institutions and systems across the continent.
+About IOM
+The International Organization for Migration, a related organization of the United Nations, is the leading intergovernmental organization in the field of migration. IOM works with governments and partners to promote safe, orderly and humane migration while strengthening health, humanitarian and development outcomes for people on the move. 
+For more information, please contact:
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:33.021571+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>IOM Saddened by Deadliest Migrant Shipwreck on West African Atlantic Route in 2026</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/iom-saddened-deadliest-migrant-shipwreck-west-african-atlantic-route-2026</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>You are currently viewing the mobile menu. To switch to the desktop version, please set your browser zoom to at least 80% or use full-screen mode.
+        Skip to main content
+        Keyboard Shortcuts
+        Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Go to Home
+ShortcutOFocus Search
+Shortcut/Language Switch
+ShortcutAFirst Main Menu Item
+ShortcutSMain Content
+ShortcutQFirst Container
+ShortcutAlt / ⌥ Option + CNext Container
+ShortcutEPrevious Container
+ShortcutWFooter Navigation
+ShortcutAlt / ⌥ Option + FContact us
+ShortcutAlt / ⌥ Option + KClick to Pause / Play all media
+ShortcutAlt / ⌥ Option + PDonate today
+ShortcutAlt / ⌥ Option + VTo open up the keyboard shortcuts
+ShortcutShift + ?
+Media is playing.
+            News
+ - 
+            Global
+22 July 2026
+Nouakchott, 22 July 2026 – The International Organization for Migration (IOM) is deeply saddened by reports that dozens of migrants are dead or missing following a shipwreck off the coast of Mauritania, where 38 survivors were rescued by the Mauritanian Coast Guard near Nouadhibou on 18 July.
+According to survivors, the vessel departed from The Gambia carrying approximately 180 people and spent 25 days at sea before rescue efforts were launched by Mauritanian coast guards and local fishermen. The survivors include men, women and children from several West African countries. One deceased person was recovered; at least 143 people are missing and are feared to have perished during the journey. Among the survivors are two children who reportedly lost their parents and younger sibling during the tragic journey.
+IOM extends its heartfelt condolences to the families of those who lost their lives and expresses its gratitude to the Mauritanian authorities, local fishing communities and all first responders involved in the rescue operation.
+"Every life lost on this route is one life too many. My thoughts are with the families who are mourning loved ones, and with the survivors who have endured an unimaginable ordeal," said Sylvia Ekra, IOM Regional Director for West and Central Africa.
+This tragedy adds to the 168 lives already lost on the West African Atlantic Route to the Canaries this year, as well as two suspected invisible shipwrecks that remain under verification and may have claimed hundreds more lives.
+This year alone, 4,440 arrivals have been recorded in the Canary Islands compared with 11,575 from January to July last year, demonstrating that the decrease in arrivals does not mean the route has become safer.
+"What this incident shows is that a decline in arrivals does not mean the route has become safer. People continue to risk everything because the pressures that drive these journeys remain. Saving lives requires a collective effort that goes beyond search and rescue. We need stronger cooperation all along the route, from countries of origin to countries of transit and destination, with greater investment in protection, opportunities closer to home, and expanded access to safe and regular pathways", said IOM’s Ekra.
+The incident underscores the urgent need for strengthened regional cooperation and sustained efforts to prevent further loss of life along migration routes across West and Northwest Africa.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+ Afghanistan
+ Albania
+ Algeria
+ Angola
+ Antigua and Barbuda
+ Argentina
+ Armenia
+ Aruba
+ Asia and the Pacific
+ Australia
+ Austria
+ Bahamas (The)
+ Bahrain
+ Bangladesh
+ Barbados
+ Belarus
+ Belgium
+ Belize
+ Benin
+ Bhutan
+ Bolivia (Plurinational State of)
+ Bosnia and Herzegovina
+ Botswana
+ Brazil
+ Burkina Faso
+ Cabo Verde
+ Cambodia
+ Cameroon
+ Canada
+ Central African Republic (the)
+ Chile
+ Colombia
+ Comoros (the)
+ Congo (the)
+ Costa Rica
+ Côte d'Ivoire
+ Croatia
+ Cuba
+ Cyprus
+ Czechia
+ Democratic Republic of the Congo (the)
+ Denmark
+ Djibouti
+ Dominica
+ Dominican Republic (the)
+ East, Horn and Southern Africa
+ Ecuador
+ Egypt
+ El Salvador
+ Eritrea
+ Eswatini
+ Ethiopia
+ Europe and Central Asia
+ Fiji
+ France
+ Gabon
+ Gambia (the)
+ Ghana
+ Global Office in Brussels
+ Global Office in Washington D.C.
+ Global Shared Services Centre
+ Guatemala
+ Guinea
+ Guinea-Bissau
+ Guyana
+ Honduras
+ Iceland
+ India
+ IOM Office at the United Nations
+ Iran (Islamic Republic of)
+ Ireland
+ Italy
+ Jamaica
+ Japan
+ Jordan
+ Kenya
+ Kuwait
+ Lao People's Democratic Republic (the)
+ Latvia
+ Lebanon
+ Lesotho
+ Liberia
+ Libya
+ Luxembourg
+ Madagascar
+ Malawi
+ Malaysia
+ Maldives
+ Mali
+ Malta
+ Marshall Islands (the)
+ Mauritius
+ Mexico
+ Micronesia (Federated States of)
+ Mongolia
+ Montenegro
+ Morocco
+ Mozambique
+ Myanmar
+ Nepal
+ New Zealand
+ Nigeria
+ North Macedonia
+ Norway
+ Oman
+ Pakistan
+ Palau
+ Panama
+ Papua New Guinea
+ Paraguay
+ Peru
+ Philippines (the)
+ Poland
+ Republic of Korea
+ Republic of Naoero
+ Romania
+ Rwanda
+ Saint Vincent and the Grenadines
+ Samoa
+ Sao Tome and Principe
+ Saudi Arabia
+ Senegal
+ Serbia
+ Seychelles
+ Sierra Leone
+ Slovenia
+ Solomon Islands
+ Somalia
+ South Africa
+ South Sudan
+ Spain
+ Sri Lanka
+ Subregional Office in Brussels
+ Subregional Office in Pretoria
+ Sudan (the)
+ Sweden
+ Syrian Arab Republic (the)
+ Thailand
+ Timor-Leste
+ Togo
+ Tonga
+ Trinidad and Tobago
+ Tunisia
+ Türkiye
+ Tuvalu
+ Uganda
+ United Kingdom of Great Britain and Northern Ireland (the)
+ United Republic of Tanzania (the)
+ UNSC Resolution 1244-Administered Kosovo
+ Uruguay
+ Uzbekistan
+ Vanuatu
+ Venezuela (Bolivarian Republic of)
+ Zambia
+ Zimbabwe
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:41.368959+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Workers Who Keep Country Moving: Costa Rica and IOM Expand Safe Labour Pathways</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/workers-who-keep-country-moving-costa-rica-and-iom-expand-safe-labour-pathways</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+San José, Costa Rica, 21 July 2026 — From farm fields to bus routes, migrant workers help keep Costa Rica’s economy and essential services running. During an official visit concluding today, Director General Amy Pope reaffirmed IOM’s partnership with the Government of Costa Rica to expand well-managed labour migration that supports economic growth, protects workers and strengthens regional cooperation.
+“Behind every migration policy are real people — workers, parents and families trying to build a better future,” said DG Pope. “What Costa Rica shows is that when countries create safe, regular pathways for people to work, everyone benefits: workers, employers and communities. It’s a practical approach that works.”
+The visit comes as Costa Rica continues to be recognized internationally for its leadership in migration governance and its commitment to the Global Compact for Safe, Orderly and Regular Migration. Discussions with the country’s new administration focused on labour mobility, regional cooperation and evidence-based approaches to managing migration across one of the world’s most dynamic migration corridors.
+At the centre of those discussions are the people whose work supports key sectors of the economy: agricultural workers from Panama and Nicaragua, Salvadoran bus drivers, and thousands of others who contribute their skills through regular migration pathways while maintaining strong ties to their countries of origin. A pilot labour mobility initiative between Costa Rica and El Salvador facilitated the recruitment of 12 Salvadoran bus drivers with IOM's technical support — a model that could be scaled up to help address an estimated shortage of more than 1,500 drivers in Costa Rica, while expanding regular labour mobility opportunities across the region, including for Costa Ricans seeking employment abroad.
+Labour migration was a key focus of the visit. Costa Rica’s efforts to work with employers and government institutions to regularize temporary workers in agriculture, transportation and other sectors are helping address labour needs while expanding opportunities for migrant workers. Between 2025 and 2026, more than 15,000 agricultural migrant workers obtained temporary work permits through the Migrant Labour Traceability System (SITLAM), developed by IOM, and more than 500 companies received support to recruit migrant workers through labor inclusion programs. As the country advances toward high-income status, these pathways are increasingly contributing to productivity, economic development and social cohesion.
+DG Pope also highlighted IOM’s support to Costa Rica across a range of migration priorities, including labour mobility programmes, migrant integration, voluntary return and reintegration assistance, and data-driven approaches to migration governance and border management.
+The visit reaffirmed IOM’s commitment to supporting Costa Rica as it continues to translate migration policy into practical solutions that benefit migrants, communities and economies. Costa Rica’s experience demonstrates how safe, orderly and regular migration, backed by political commitment and strong partnerships, can deliver positive outcomes for all.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:55:59.407580+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IOM.xlsx
+++ b/IOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -16868,6 +16868,46 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>League of Arab States and IOM Launch the Arab Migration Data Network</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/league-arab-states-and-iom-launch-arab-migration-data-network</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Cairo, 29 October 2026 - The League of Arab States and the International Organization for Migration (IOM) have formally launched the Arab Migration Data Network, the first Arab network dedicated to migration data. The launch took place at a signing ceremony at the headquarters of the League’s General Secretariat in Cairo, where the Network’s first Action Plan (2026-2028) was first adopted.
+The Network is a regional mechanism for technical cooperation led by Arab States. For the first time, it brings together national statistical offices and government entities responsible for migration data across all 22 Arab States within a permanent framework for joint action.
+The 22 Arab States host approximately 44.5 million international migrants, around 14.7 per cent of the global total, while 37.2 million people from Arab countries live outside their countries of origin, about half of them in other Arab States. Yet migration data remain spread across multiple institutions and continue to face challenges in coverage, timeliness and comparability.
+The Network will help Arab States harmonize concepts and methodologies, exchange expertise, and build a clearer picture of migration across countries of origin, transit, destination and return.
+The Action Plan was signed by H.E. Minister Plenipotentiary Abeer Al-Jalahma, Director of the Statistics and Databases Department at the League of Arab States, and Mr. Justin MacDermott, IOM Deputy Regional Director for Operations for the Middle East and North Africa. The ceremony was attended by ambassadors and representatives of diplomatic missions, directors-general of national statistical offices, senior government officials, and regional and international partners.
+It concluded a two-day Senior Officials Meeting on Strengthening Migration Data in the Arab Region (27-28 October), which brought together high-level representatives from 13 Arab States: Algeria, Bahrain, Egypt, Iraq, Jordan, Libya, Mauritania, Morocco, Qatar, Saudi Arabia, Sudan, Tunisia and Yemen. Participants discussed priorities for joint action and helped shape the Action Plan ahead of its adoption.
+“The launch of the Arab Migration Data Network marks a milestone in the journey of joint Arab statistical cooperation. For the first time, our countries are coming together around a permanent platform dedicated to migration data, led by Arab States and driven by their priorities. What we have built today is not simply a new initiative, but a shared Arab statistical language that serves decision-makers and reflects the realities of our people,” said H.E. Minister Plenipotentiary Abeer Al-Jalahma.
+For IOM, Justin MacDermott noted: “The launch of the Arab Migration Data Network is not the culmination of our efforts; it is the beginning of a new chapter in regional cooperation, built on trust, shared knowledge, national ownership and collective action.”
+Under the Action Plan, the Network will:
+Arab States showed clear commitment from the outset, with 10 countries already designating national focal points. Delegations also presented practical proposals to further develop the Network’s working mechanisms.
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:16:21.598430+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IOM.xlsx
+++ b/IOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E351"/>
+  <dimension ref="A1:E352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -16908,6 +16908,45 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1.3 Million Return to Afghanistan as Winter Threatens Vulnerable Families</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://www.iom.int/news/13-million-return-afghanistan-winter-threatens-vulnerable-families</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Note: If you are using a screen reader, you may need to use the pass-through key (or pass key) to allow some of these keyboard shortcuts to work as intended.
+Geneva/Kabul, 30 October 2026 – More than 1.3 million Afghans have returned from the Islamic Republic of Iran and Pakistan this year, as an USD 8.8 million inter-agency funding gap threatens winter assistance for vulnerable families facing inadequate shelter, heating and other essential supplies such as winter support, the International Organization for Migration (IOM) warned on Friday.
+“Families are returning to communities where housing and basic services are already under severe strain. Winter is now adding another urgent need,” said Mihyung Park, IOM’s Chief of Mission in Afghanistan. “We need funding now to help families find shelter and keep warm before snow cuts access to remote areas.” 
+The growing number of returnees is placing additional pressure on already overstretched communities. Since September 2023, more than 6.6 million returns have been recorded, including 2.9 million in 2025 and 1.3 million so far in 2026, according to the IOM-led Border Consortium.  
+Many families do not have access to safe shelter, heating, fuel, warm clothing or blankets. The 2026–2027 winter response plan of the Shelter, Land and Site Coordination Cluster in Afghanistan, which IOM co-leads with UNHCR, aims to assist nearly 200,000 people but has received only USD 4 million of the USD 12.8 million required. Without further funding, more than 140,000 vulnerable people, including returnees, displaced and host communities, could be left without critical winter assistance and exposed to potentially deadly cold. 
+Afghanistan also faces an increased risk of heavy rain and snowfall this winter. The inter-agency Afghanistan El Niño Preparedness Plan 2026-2027 estimates that a strong El Niño event could bring above-average precipitation between October and April next year. 
+Winter will also make it harder to reach families in many parts of Afghanistan. IOM’s 2025 Afghanistan Climate Vulnerability Assessment found that nearly one quarter of communities have limited access to heating. It also found that 73 per cent rely on unpaved roads, more than a third of which become inaccessible during winter, making it increasingly difficult to deliver assistance to remote areas.  
+Returnees are not the only families in need of shelter this winter. Roughly 15,000 homes were damaged or destroyed in 2025 by floods and the earthquake centered in Kunar province. Across 183 districts where this damage was reported, families are living in inadequate conditions and are exposed to harsh winter conditions.  
+IOM is calling for immediate support to close the USD 8.8 million inter-agency funding gap and deliver emergency shelter, winter supplies and essential household items before severe weather cuts off access to vulnerable communities, displaced people and returnees.
+Send emergency aid to families in need: Donate here 
+For more information, please visit IOM’s Media Centre.
+With your help, IOM can save lives by delivering crucial assistance wherever and whenever it is needed most.
+We use cookies and other identifiers to help improve your online experience. By using our website, you agree to this. To find out what cookies are used for, read our</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:02.304698+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
